--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -62,17 +62,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -101,6 +106,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -643,47 +649,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>14/09/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>016/2026</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecuc ión de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>02/10/2026</t>
-        </is>
-      </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -691,11 +697,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>$ 100.000, 00.- (PESOS CIEN MIL CON 00/100)</t>
-        </is>
-      </c>
+      <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -713,14 +715,14 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-53f1430f94acb0b0</t>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -728,44 +730,44 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MINISTERIO DE SALUD</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Licitación Publica</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Minister io de Salud, sito en calle 25 de Mayo N° 181, segundo p</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -781,19 +783,19 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-3312d89e1a3e2e53</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -801,14 +803,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -818,22 +820,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>31/2026</t>
+          <t>01-2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>07 de octubre de 2026 Hora: 10:00</t>
+          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -841,7 +843,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -859,7 +865,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-76d9566cb30a6df5</t>
+          <t>id-28313c7a9524d0ee</t>
         </is>
       </c>
     </row>
@@ -874,39 +880,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -914,7 +920,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+        </is>
+      </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -927,12 +937,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -947,14 +957,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -964,22 +974,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -987,7 +997,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1005,7 +1019,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
@@ -1020,14 +1034,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1037,22 +1051,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1060,11 +1074,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+      <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1077,12 +1087,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1109,12 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1114,22 +1124,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1137,11 +1147,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Gratuito</t>
-        </is>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1159,7 +1165,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1174,14 +1180,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1191,22 +1197,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1216,7 +1222,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1236,7 +1242,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1251,14 +1257,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1268,22 +1274,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1293,7 +1299,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>Gratuito</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1313,7 +1319,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1328,14 +1334,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1345,12 +1351,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1360,7 +1366,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1368,7 +1374,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1381,12 +1391,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1418,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1418,22 +1428,22 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1443,7 +1453,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -1463,7 +1473,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1478,14 +1488,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1493,20 +1503,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1514,11 +1528,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+      <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1531,12 +1541,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1568,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1568,30 +1578,34 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1609,7 +1623,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1624,14 +1638,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1639,14 +1653,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>09/2026</t>
-        </is>
-      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1656,15 +1666,19 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1677,19 +1691,19 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1697,14 +1711,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1714,27 +1728,27 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
@@ -1755,7 +1769,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1770,51 +1784,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1827,12 +1837,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -1847,49 +1857,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1904,12 +1914,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1924,14 +1934,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1941,22 +1951,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1966,7 +1976,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1986,7 +1996,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2018,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2018,12 +2028,12 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2033,7 +2043,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2041,7 +2051,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2054,12 +2068,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2069,9 +2083,9 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2081,7 +2095,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2091,18 +2105,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2110,11 +2128,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2127,12 +2141,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2147,14 +2161,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2164,18 +2178,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2183,7 +2197,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2201,7 +2219,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2216,14 +2234,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2233,12 +2251,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -2270,7 +2288,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2285,14 +2303,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2302,18 +2320,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2321,11 +2339,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2338,12 +2352,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2372,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2380,13 +2394,13 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2394,7 +2408,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2412,14 +2430,14 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2429,29 +2447,33 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2472,12 +2494,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2514,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2561,7 +2583,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
@@ -2757,146 +2779,8 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>232/26</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>id-5a01c3fd726f10dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>228/26</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>id-e125fe54abc33d69</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O33"/>
+  <autoFilter ref="A1:O31"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -2958,10 +2842,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -737,32 +737,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>01-2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -770,7 +770,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -783,12 +787,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-28313c7a9524d0ee</t>
         </is>
       </c>
     </row>
@@ -803,14 +807,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -820,12 +824,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>01-2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -835,7 +839,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -845,7 +849,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -865,7 +869,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-28313c7a9524d0ee</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -880,14 +884,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -897,12 +901,12 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -912,7 +916,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -922,7 +926,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -942,7 +946,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
@@ -964,7 +968,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -974,12 +978,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -997,11 +1001,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1034,14 +1034,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1051,22 +1051,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1107,14 +1107,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1124,22 +1124,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1147,7 +1147,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1165,7 +1169,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1191,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1197,12 +1201,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1212,7 +1216,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1222,7 +1226,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+          <t>Gratuito</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1242,7 +1246,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1257,14 +1261,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1274,22 +1278,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1299,7 +1303,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Gratuito</t>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1319,7 +1323,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1334,14 +1338,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1351,12 +1355,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1366,7 +1370,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1376,7 +1380,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1396,7 +1400,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1422,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1428,12 +1432,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1443,7 +1447,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1451,11 +1455,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1528,7 +1528,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1541,12 +1545,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1561,14 +1565,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1576,24 +1580,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1638,14 +1638,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1653,10 +1653,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1666,19 +1670,15 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -1784,47 +1784,51 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1837,12 +1841,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1857,49 +1861,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1914,12 +1918,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -1934,14 +1938,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1951,22 +1955,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1976,7 +1980,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1996,7 +2000,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2022,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2028,12 +2032,12 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2043,7 +2047,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2051,11 +2055,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2083,9 +2083,9 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2105,22 +2105,18 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2128,7 +2124,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2161,14 +2161,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2178,18 +2178,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2197,11 +2197,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2219,7 +2215,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2234,14 +2230,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -2288,14 +2284,14 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2303,14 +2299,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2320,18 +2316,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2352,19 +2348,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2389,18 +2385,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2408,11 +2404,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2430,14 +2422,14 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2462,18 +2454,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2499,14 +2491,14 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2521,28 +2513,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2563,19 +2555,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2583,35 +2575,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2632,19 +2624,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2652,14 +2644,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2667,20 +2659,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2701,19 +2689,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2721,35 +2709,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2770,17 +2758,703 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>id-34c85bcdb9b1123f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IAPV (Vivienda)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Publicada 08/10/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>id-75bfffae63b7eedc</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>IAPV (Vivienda)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Publicada 06/10/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>id-07ddb93a12c5a870</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>IAPV (Vivienda)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Concurso de Precio N° 02/2025</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Publicada 19/06/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>id-7c1bf02160a66f67</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>id-654eebef400f89cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>id-9a16884dd5a64a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>id-0691eb485d7548eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>10-2026</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>228/26</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>id-e125fe54abc33d69</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>230/26</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>“Provisión de manteriales y contratación del servicio de reparación de dos ascensores centrales ubicados en Edificio Tribunales de Concepción del Uruguay de calle San Martín Nº 665”</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>id-8ba9b58bf86dac2c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O31"/>
+  <autoFilter ref="A1:O41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -2842,6 +3516,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -657,14 +657,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>016/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Av enida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-53f1430f94acb0b0</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Áridos</t>
         </is>
@@ -957,7 +957,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1184,7 +1184,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1411,7 +1411,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1926,7 +1926,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1941,22 +1941,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1966,19 +1966,15 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1991,12 +1987,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -2011,49 +2007,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2068,12 +2064,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2088,14 +2084,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2105,22 +2101,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2130,7 +2126,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2150,7 +2146,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2168,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2182,12 +2178,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2197,7 +2193,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2205,7 +2201,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2233,9 +2233,9 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2255,18 +2255,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2274,11 +2278,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2311,14 +2311,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2328,18 +2328,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2347,7 +2347,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2365,7 +2369,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2380,14 +2384,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2397,12 +2401,12 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2449,29 +2453,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Boletín Oficial</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -2503,7 +2507,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-e90021854bcee649</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2522,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2591,7 +2595,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2652,7 +2656,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2660,9 +2664,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2672,17 +2676,13 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2729,29 +2729,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2798,35 +2798,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -2879,17 +2879,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2921,12 +2921,219 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>232/26</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>id-5a01c3fd726f10dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>228/26</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>id-e125fe54abc33d69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O33"/>
+  <autoFilter ref="A1:O36"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -2992,6 +3199,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,7 +101,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -649,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -659,12 +653,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Áridos</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -674,22 +668,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>016/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Av enida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -697,7 +691,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -715,7 +713,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-53f1430f94acb0b0</t>
         </is>
       </c>
     </row>
@@ -807,7 +805,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -884,7 +882,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -961,7 +959,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1034,7 +1032,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1107,7 +1105,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
@@ -1184,7 +1182,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
@@ -1261,7 +1259,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1338,7 +1336,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1415,7 +1413,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1488,7 +1486,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1565,7 +1563,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
@@ -1638,7 +1636,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1711,7 +1709,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1776,7 +1774,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1784,29 +1782,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1816,19 +1814,15 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1841,12 +1835,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -1861,49 +1855,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1918,12 +1912,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1938,14 +1932,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1955,22 +1949,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1980,7 +1974,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -2000,7 +1994,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2015,14 +2009,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2032,12 +2026,12 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2047,7 +2041,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2055,7 +2049,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2068,12 +2066,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2083,19 +2081,19 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2105,18 +2103,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2124,11 +2126,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2141,12 +2139,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2161,14 +2159,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2178,18 +2176,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2197,7 +2195,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2215,7 +2217,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2230,14 +2232,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2247,12 +2249,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -2284,14 +2286,14 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2299,14 +2301,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2316,18 +2318,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2348,12 +2350,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2370,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2385,18 +2387,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2422,7 +2424,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2439,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2454,18 +2456,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2491,7 +2493,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2508,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2523,18 +2525,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2560,7 +2562,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2577,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2592,18 +2594,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2629,7 +2631,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2646,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2659,16 +2661,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2694,7 +2700,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2715,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2724,20 +2730,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>04/2025</t>
-        </is>
-      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2763,7 +2765,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2780,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2795,18 +2797,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2832,14 +2834,14 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2847,7 +2849,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2864,18 +2866,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2901,7 +2903,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2918,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2938,13 +2940,13 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2970,14 +2972,14 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2985,31 +2987,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3030,19 +3036,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3050,9 +3056,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3062,17 +3068,13 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -3104,7 +3106,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -3119,29 +3121,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -3168,12 +3170,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3190,33 +3192,33 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3237,12 +3239,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3259,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -3269,17 +3271,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -3311,14 +3313,14 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3328,33 +3330,33 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>228/26</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3375,19 +3377,19 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-e125fe54abc33d69</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3395,7 +3397,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -3412,12 +3414,12 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>230/26</t>
+          <t>232/26</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>“Provisión de manteriales y contratación del servicio de reparación de dos ascensores centrales ubicados en Edificio Tribunales de Concepción del Uruguay de calle San Martín Nº 665”</t>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -3449,12 +3451,81 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-8ba9b58bf86dac2c</t>
+          <t>id-5a01c3fd726f10dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>228/26</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>id-e125fe54abc33d69</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3536,6 +3607,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -63,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,7 +101,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -679,7 +673,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Av enida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -699,7 +693,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+          <t>$ 100.000, 00.- (PESOS CIEN MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -734,29 +728,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -766,7 +760,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -787,12 +781,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
@@ -814,32 +808,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>01-2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -847,7 +841,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -860,12 +858,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-28313c7a9524d0ee</t>
         </is>
       </c>
     </row>
@@ -880,14 +878,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -897,12 +895,12 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>01-2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -912,7 +910,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -922,7 +920,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -942,7 +940,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-28313c7a9524d0ee</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -957,14 +955,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -974,12 +972,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -989,7 +987,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -999,7 +997,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -1019,7 +1017,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
@@ -1034,14 +1032,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1051,12 +1049,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1066,7 +1064,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1074,11 +1072,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1091,12 +1085,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1111,14 +1105,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1128,22 +1122,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1164,12 +1158,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1184,14 +1178,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1201,22 +1195,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1224,7 +1218,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1242,7 +1240,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1257,14 +1255,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1274,12 +1272,12 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1289,7 +1287,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1299,7 +1297,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+          <t>Gratuito</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1319,7 +1317,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1334,14 +1332,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1351,22 +1349,22 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1376,7 +1374,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Gratuito</t>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1396,7 +1394,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1411,14 +1409,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1428,12 +1426,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1443,7 +1441,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1453,7 +1451,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -1473,7 +1471,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1488,14 +1486,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1505,12 +1503,12 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1520,7 +1518,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1528,11 +1526,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1545,12 +1539,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1565,14 +1559,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1582,22 +1576,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1605,7 +1599,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1618,12 +1616,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1638,12 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1653,24 +1651,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1680,7 +1674,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1700,7 +1694,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1715,14 +1709,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1730,10 +1724,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1743,19 +1741,15 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1773,7 +1767,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1788,14 +1782,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1805,12 +1799,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1820,7 +1814,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1841,19 +1835,19 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1863,12 +1857,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1878,27 +1872,27 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado caj ón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -1914,19 +1908,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1934,29 +1928,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1966,15 +1960,19 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1987,12 +1985,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2007,49 +2005,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2064,12 +2062,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2084,14 +2082,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2101,22 +2099,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2126,7 +2124,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2146,7 +2144,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2161,14 +2159,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2178,12 +2176,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2193,7 +2191,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2201,11 +2199,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2218,12 +2212,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2233,19 +2227,19 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2255,22 +2249,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2278,7 +2268,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2291,12 +2285,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2313,12 +2307,12 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2328,18 +2322,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2347,11 +2341,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2369,7 +2359,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2384,14 +2374,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2401,12 +2391,12 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -2438,7 +2428,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2453,14 +2443,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2470,18 +2460,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2489,7 +2479,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2502,12 +2496,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2544,13 +2538,13 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2558,11 +2552,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2580,14 +2570,14 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2595,35 +2585,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2644,19 +2630,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2664,9 +2650,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2676,13 +2662,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -2714,7 +2704,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2729,29 +2719,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -2778,12 +2768,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -2798,35 +2788,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2847,12 +2837,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2857,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -2879,17 +2869,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2921,14 +2911,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2936,35 +2926,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>232/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2985,12 +2975,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-5a01c3fd726f10dc</t>
         </is>
       </c>
     </row>
@@ -3005,9 +2995,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3022,12 +3012,12 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>232/26</t>
+          <t>228/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
+          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -3059,81 +3049,12 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-5a01c3fd726f10dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>228/26</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
           <t>id-e125fe54abc33d69</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O36"/>
+  <autoFilter ref="A1:O35"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3203,8 +3124,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Av enida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+          <t>$ 100.000, 00.- (PESOS CIEN MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -728,14 +728,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -745,22 +745,22 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>01-2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -768,11 +768,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -790,7 +786,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-28313c7a9524d0ee</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -805,14 +801,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -822,22 +818,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -847,7 +843,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -867,7 +863,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -884,12 +880,12 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -899,22 +895,22 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -924,7 +920,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>Gratuito</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -944,7 +940,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -959,14 +955,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -976,22 +972,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -999,7 +995,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1032,14 +1032,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1072,7 +1072,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1090,7 +1094,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1111,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1122,22 +1126,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1145,11 +1149,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Gratuito</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1259,14 +1259,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1274,24 +1274,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>015/2026</t>
-        </is>
-      </c>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1301,7 +1297,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1321,7 +1317,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1336,14 +1332,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1353,34 +1349,30 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1398,7 +1390,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1413,14 +1405,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1435,22 +1427,22 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1466,19 +1458,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1488,12 +1480,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1503,34 +1495,30 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado caj ón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1548,7 +1536,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -1563,45 +1551,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>5/2026</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -1616,12 +1608,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1636,14 +1628,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1653,30 +1645,34 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1694,7 +1690,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -1709,14 +1705,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1726,30 +1722,34 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1762,19 +1762,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1799,27 +1799,27 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -1850,54 +1850,50 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1912,12 +1908,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -1927,19 +1923,19 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1949,22 +1945,18 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1972,11 +1964,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1994,7 +1982,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2004,19 +1992,19 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2026,22 +2014,18 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2049,11 +2033,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2071,29 +2051,29 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2103,22 +2083,18 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2139,19 +2115,19 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2159,14 +2135,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2176,18 +2152,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2195,11 +2171,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2212,19 +2184,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2232,14 +2204,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2249,18 +2221,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2281,19 +2253,19 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2301,14 +2273,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2318,18 +2290,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2350,12 +2322,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2387,18 +2359,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2424,7 +2396,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2454,20 +2426,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>02/2026</t>
-        </is>
-      </c>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2493,7 +2461,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -2525,18 +2493,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2562,7 +2530,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -2594,18 +2562,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2631,14 +2599,14 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2663,18 +2631,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2700,14 +2668,14 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2730,16 +2698,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2765,7 +2737,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2780,35 +2752,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>04/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2829,19 +2797,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2856,28 +2824,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2898,19 +2866,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2918,35 +2886,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>232/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2967,19 +2935,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-5a01c3fd726f10dc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2994,28 +2962,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>228/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3036,19 +3004,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-e125fe54abc33d69</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3056,25 +3024,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -3101,12 +3073,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -3121,35 +3093,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3170,12 +3142,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -3192,33 +3164,33 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3239,293 +3211,17 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>id-bdd0abb0374c3f42</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>04-2026</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>232/26</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>id-5a01c3fd726f10dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>228/26</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>id-e125fe54abc33d69</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3601,14 +3297,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecuc ión de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -728,44 +728,44 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Minister io de Salud, sito en calle 25 de Mayo N° 181, segundo p</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -781,19 +781,19 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -801,14 +801,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
+          <t>MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -818,22 +818,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>01-2026</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -841,11 +841,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -863,7 +859,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-28313c7a9524d0ee</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
@@ -878,39 +874,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -918,11 +914,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
-        </is>
-      </c>
+      <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -935,12 +927,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
@@ -955,14 +947,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -972,22 +964,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -995,11 +987,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1017,7 +1005,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1022,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1049,22 +1037,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1072,7 +1060,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1085,12 +1077,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1097,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1122,22 +1114,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1145,7 +1137,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Gratuito</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1163,7 +1159,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1178,14 +1174,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1195,22 +1191,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1220,7 +1216,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1240,7 +1236,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1253,12 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1272,22 +1268,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Gratuito</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1317,7 +1313,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1332,14 +1328,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1349,12 +1345,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1364,7 +1360,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1372,11 +1368,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1389,12 +1381,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1409,14 +1401,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1426,22 +1418,22 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1451,7 +1443,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -1471,7 +1463,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1480,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1501,24 +1493,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>09/2026</t>
-        </is>
-      </c>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1526,7 +1514,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1539,12 +1531,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1559,14 +1551,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1576,34 +1568,30 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1621,7 +1609,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1626,12 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1651,10 +1639,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1664,19 +1656,15 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1689,19 +1677,19 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1711,12 +1699,12 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1726,27 +1714,27 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
@@ -1767,7 +1755,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -1784,45 +1772,49 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1835,19 +1827,19 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1855,14 +1847,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1872,30 +1864,34 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado caj ón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1913,7 +1909,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -1930,47 +1926,47 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1985,12 +1981,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2005,14 +2001,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2022,22 +2018,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2045,11 +2041,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2062,12 +2054,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2077,19 +2069,19 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2099,22 +2091,18 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2124,7 +2112,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2144,7 +2132,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2154,19 +2142,19 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2176,22 +2164,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2212,12 +2196,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2232,14 +2216,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2249,18 +2233,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2268,11 +2252,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2290,7 +2270,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2305,14 +2285,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2322,18 +2302,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2341,7 +2321,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2354,12 +2338,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2374,14 +2358,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2391,18 +2375,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2423,19 +2407,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2443,35 +2427,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2479,11 +2459,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2496,12 +2472,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2523,28 +2499,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2565,19 +2541,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2585,25 +2561,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2630,12 +2610,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -2650,35 +2630,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2699,12 +2679,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -2721,33 +2701,33 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2768,19 +2748,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2788,35 +2768,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>232/26</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2837,19 +2817,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-5a01c3fd726f10dc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2857,35 +2837,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>228/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2906,155 +2886,17 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>232/26</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>id-5a01c3fd726f10dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>228/26</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr"/>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
           <t>id-e125fe54abc33d69</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O35"/>
+  <autoFilter ref="A1:O33"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3120,10 +2962,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+          <t>$ 100.000, 00.- (PESOS CIEN MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -720,55 +720,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>06/26</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>P ARANA — MINISTERIO DE SALUD</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Licitación Publica</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>17/26</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -786,54 +790,54 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-3312d89e1a3e2e53</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>08-2026</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>31/2026</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>07 de octubre de 2026 Hora: 10:00</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -841,7 +845,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Gratuito</t>
+        </is>
+      </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -859,14 +867,14 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-76d9566cb30a6df5</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -874,14 +882,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -891,30 +899,34 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -932,14 +944,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -947,14 +959,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -964,30 +976,34 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C . P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1005,14 +1021,14 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1020,14 +1036,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1037,27 +1053,27 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1073,12 +1089,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1111,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1110,22 +1126,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1135,7 +1151,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -1155,7 +1171,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1170,14 +1186,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1185,24 +1201,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>08-2026</t>
-        </is>
-      </c>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1212,7 +1224,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Gratuito</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1232,7 +1244,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1247,14 +1259,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1264,34 +1276,30 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1309,7 +1317,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1332,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1341,34 +1349,30 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1386,14 +1390,14 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1403,12 +1407,12 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1418,27 +1422,27 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado caj ón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1454,12 +1458,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -1476,47 +1480,47 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -1531,12 +1535,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1551,14 +1555,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1566,20 +1570,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1589,7 +1597,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -1609,7 +1617,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -1624,14 +1632,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1641,30 +1649,34 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1682,7 +1694,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -1697,14 +1709,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1714,27 +1726,27 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
@@ -1750,34 +1762,34 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1787,30 +1799,30 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1828,7 +1840,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -1838,56 +1850,48 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1900,12 +1904,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -1915,9 +1919,9 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1927,7 +1931,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1937,22 +1941,18 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1960,11 +1960,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1982,29 +1978,29 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2014,22 +2010,18 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2037,11 +2029,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2054,34 +2042,34 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2091,22 +2079,18 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2127,19 +2111,19 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2147,14 +2131,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2164,18 +2148,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2183,11 +2167,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2200,19 +2180,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2220,14 +2200,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2237,18 +2217,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2269,19 +2249,19 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2289,14 +2269,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2306,18 +2286,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2338,19 +2318,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2373,20 +2353,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2394,11 +2370,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2416,14 +2388,14 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2448,18 +2420,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2485,7 +2457,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -2500,31 +2472,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2545,12 +2521,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -2572,28 +2548,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2614,12 +2590,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2634,35 +2610,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2683,19 +2659,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2705,33 +2681,29 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2752,12 +2724,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2772,35 +2744,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2821,19 +2793,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2841,7 +2813,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -2858,12 +2830,12 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>232/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2895,14 +2867,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
+          <t>id-5a01c3fd726f10dc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2910,9 +2882,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2922,17 +2894,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>04/26</t>
+          <t>228/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
+          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -2964,14 +2936,14 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-2466cef612391e08</t>
+          <t>id-e125fe54abc33d69</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2981,33 +2953,33 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>232/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3028,17 +3000,155 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-5a01c3fd726f10dc</t>
+          <t>id-0691eb485d7548eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>10-2026</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O35"/>
+  <autoFilter ref="A1:O37"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3108,6 +3218,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>$ 100.000, 00.- (PESOS CIEN MIL CON 00/100)</t>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -735,37 +735,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>P ARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -786,14 +786,14 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -801,14 +801,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -818,22 +818,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -841,11 +841,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+      <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -863,14 +859,14 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -880,12 +876,12 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -895,34 +891,30 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>Gratuito</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -940,14 +932,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -955,14 +947,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -972,34 +964,30 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>REPARACIONES VARIAS EN C . P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1017,14 +1005,14 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1032,14 +1020,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1049,34 +1037,30 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1094,7 +1078,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1095,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1126,22 +1110,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1149,7 +1133,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1162,12 +1150,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1172,12 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1199,22 +1187,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1224,7 +1212,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>Gratuito</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1244,7 +1232,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1259,14 +1247,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1274,20 +1262,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>015/2026</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1297,7 +1289,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1317,7 +1309,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1332,14 +1324,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1349,30 +1341,34 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1390,7 +1386,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1405,14 +1401,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1427,22 +1423,22 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1458,19 +1454,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1480,12 +1476,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1495,30 +1491,34 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado caj ón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1551,49 +1551,45 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>5/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -1608,12 +1604,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1628,14 +1624,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1645,34 +1641,30 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1690,7 +1682,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1705,14 +1697,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1722,34 +1714,30 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1762,19 +1750,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1784,12 +1772,12 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1799,27 +1787,27 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -1835,12 +1823,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -1850,50 +1838,54 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1908,12 +1900,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1923,19 +1915,19 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1945,18 +1937,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1964,7 +1960,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -1992,19 +1992,19 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2014,18 +2014,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2033,7 +2037,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2051,29 +2059,29 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2083,18 +2091,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2115,19 +2127,19 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2135,14 +2147,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2152,18 +2164,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2171,7 +2183,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2184,19 +2200,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2204,14 +2220,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2221,18 +2237,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2253,19 +2269,19 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2273,14 +2289,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2290,18 +2306,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2322,19 +2338,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2359,18 +2375,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2378,7 +2394,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2396,14 +2416,14 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2426,16 +2446,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2461,7 +2485,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2476,35 +2500,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>04/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2525,19 +2545,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2552,28 +2572,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2594,12 +2614,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2614,35 +2634,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2663,12 +2683,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -2683,14 +2703,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2700,18 +2720,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2732,19 +2752,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2754,29 +2774,33 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2797,19 +2821,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2817,35 +2841,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>233/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2866,19 +2890,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-f48b8e7889aac66c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2886,7 +2910,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -2898,17 +2922,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>232/26</t>
+          <t>04/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
+          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -2940,14 +2964,14 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-5a01c3fd726f10dc</t>
+          <t>id-2466cef612391e08</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2955,9 +2979,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2972,12 +2996,12 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>228/26</t>
+          <t>232/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -3009,219 +3033,12 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-e125fe54abc33d69</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t>id-0691eb485d7548eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>id-bdd0abb0374c3f42</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>04-2026</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="inlineStr">
-        <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-5a01c3fd726f10dc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O38"/>
+  <autoFilter ref="A1:O35"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3291,12 +3108,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>$ 100.000, 00.- (PESOS CIEN MIL CON 00/100)</t>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -728,51 +728,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>P ARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -790,14 +786,14 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -805,14 +801,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -822,22 +818,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -845,11 +841,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>Gratuito</t>
-        </is>
-      </c>
+      <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -867,14 +859,14 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -882,14 +874,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -899,34 +891,30 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -944,14 +932,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -959,14 +947,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -976,34 +964,30 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>REPARACIONES VARIAS EN C . P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1021,14 +1005,14 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1036,14 +1020,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1053,27 +1037,27 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1089,19 +1073,19 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1111,12 +1095,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1126,22 +1110,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1151,7 +1135,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -1171,14 +1155,14 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1186,14 +1170,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1201,20 +1185,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>08-2026</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1224,7 +1212,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>Gratuito</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1244,14 +1232,14 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1259,14 +1247,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1276,30 +1264,34 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1317,14 +1309,14 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1332,14 +1324,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1349,30 +1341,34 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1390,14 +1386,14 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1407,12 +1403,12 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1422,27 +1418,27 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado caj ón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1458,19 +1454,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1480,47 +1476,47 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -1535,19 +1531,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1555,39 +1551,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>304/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1595,11 +1591,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1612,19 +1604,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1632,39 +1624,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>82/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1672,11 +1664,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1689,19 +1677,19 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1711,12 +1699,12 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1724,24 +1712,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1749,7 +1733,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1762,34 +1750,34 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1799,30 +1787,30 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1840,29 +1828,29 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1872,23 +1860,27 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -1904,34 +1896,34 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1941,23 +1933,27 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -1978,58 +1974,66 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2042,34 +2046,34 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2079,18 +2083,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2098,7 +2106,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2111,34 +2123,34 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2148,18 +2160,22 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2167,7 +2183,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2180,34 +2200,34 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2217,18 +2237,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2249,19 +2273,19 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2269,14 +2293,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2286,18 +2310,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2305,7 +2329,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2318,19 +2346,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2338,14 +2366,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2353,16 +2381,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2383,19 +2415,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2403,14 +2435,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2420,18 +2452,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2452,19 +2484,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2489,18 +2521,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2508,7 +2540,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2526,14 +2562,14 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2563,13 +2599,13 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2595,14 +2631,14 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2610,35 +2646,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2659,19 +2691,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2679,9 +2711,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2691,13 +2723,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -2729,14 +2765,14 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2744,29 +2780,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -2793,19 +2829,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2813,35 +2849,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>232/26</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2862,19 +2898,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-5a01c3fd726f10dc</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2882,35 +2918,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>228/26</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización Nº 228/26, porContratación del servicio de recarga, revisión, prueba hidráulica y mantenimiento de los matafuegos ubicados en los Edificios de calle San Martín Nº15, Mitre Nº581 y Sarmiento Nº356 de la localidad de Victoria</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2931,19 +2967,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-e125fe54abc33d69</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2953,33 +2989,33 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>233/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3000,19 +3036,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-f48b8e7889aac66c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3020,35 +3056,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>04/26</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3069,19 +3105,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-2466cef612391e08</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3089,35 +3125,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>232/26</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3138,12 +3174,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-5a01c3fd726f10dc</t>
         </is>
       </c>
     </row>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -2780,35 +2780,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -2861,17 +2861,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
@@ -2925,28 +2925,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>233/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-f48b8e7889aac66c</t>
         </is>
       </c>
     </row>
@@ -2999,17 +2999,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>04/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
+          <t>id-2466cef612391e08</t>
         </is>
       </c>
     </row>
@@ -3068,17 +3068,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>04/26</t>
+          <t>232/26</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-2466cef612391e08</t>
+          <t>id-5a01c3fd726f10dc</t>
         </is>
       </c>
     </row>
@@ -3125,35 +3125,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>232/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-5a01c3fd726f10dc</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -70,16 +75,6 @@
         <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -93,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,7 +101,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -582,12 +576,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>COLON — MUNICIPALIDAD DE VILLA ELISA (E.R.)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -597,22 +591,22 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>016/2026</t>
+          <t>004/26</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
+          <t>ADQUISICIÓN DE UN (1) VEHÍCULO PARA TRANSPORTE DE PASAJEROS DE (5) CINCO PLAZAS 0 KM - MODELO/AÑO 2026, PARA LA MUNICIPALIDAD DE LA CIUDAD DE VILLA ELISA, ENTRE RÍOS</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>01 de OCTUBRE de 2026 a la hora 10:00 en la Oficina de Compras de la Municipalidad de Villa Elisa, Entre Ríos</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -622,7 +616,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+          <t xml:space="preserve">$ 20.000,00 (Pesos Veinte mil con 00/100) el que se puede adquirir en </t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
@@ -642,14 +636,14 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>id-53f1430f94acb0b0</t>
+          <t>id-0132097e777a3442</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -659,12 +653,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -674,22 +668,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>016/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026 HORA: 11:00 HS</t>
+          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -699,7 +693,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -719,7 +713,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-65d18d99bf0b2c6c</t>
+          <t>id-53f1430f94acb0b0</t>
         </is>
       </c>
     </row>
@@ -734,14 +728,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE SALUD</t>
+          <t>P ARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -807,14 +801,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -872,7 +866,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -882,12 +876,12 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -897,27 +891,27 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>32/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 10:00</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -938,14 +932,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-0ace7de8f16d3baf</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -953,14 +947,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -970,27 +964,27 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>33/2026</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>REPARACIONES VARIAS EN C . P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 11:00</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
@@ -1011,14 +1005,14 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-fe71ac2aaf71b8d8</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1026,14 +1020,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1043,27 +1037,27 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>34/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>09 de octubre de 2026 Hora: 10:00</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1084,54 +1078,54 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-b147fbd9d3081bfc</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>015/2026</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1141,7 +1135,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -1161,54 +1155,54 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>09/26</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MUNICIPALIDAD DE SANTA ELENA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>11/2026</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10: 00 HS</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1218,7 +1212,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1238,7 +1232,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-1a2561509308b1b6</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1253,14 +1247,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1270,27 +1264,27 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
@@ -1306,12 +1300,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1326,14 +1320,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1343,30 +1337,34 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1384,7 +1382,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1401,42 +1399,42 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>304/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1452,19 +1450,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1472,35 +1470,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE COLON</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
+          <t>LICITACIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>82/2026</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES ELÉCTRICOS PARA EJECUCIÓN DEL PROYECTO DE RECONVERSIÓN Y OPTIMIZACIÓN DEL ALUMBRADO PÚBLICO DE LA CIUDAD DE COLÓN”</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>14 de OCTUBRE de 2026</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1508,11 +1510,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+      <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1525,19 +1523,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-9e122d52de12ffef</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1545,14 +1543,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DIAMANTE — COMUNA ALDEA PROTESTANTE -- DIAMANTE -- ENTRE RÍOS</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1560,24 +1558,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>03/2026</t>
-        </is>
-      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Conforme a lo autorizado por decreto Nº 290/26 llámese a licitación pública Nº 03/26 con el objeto de comprar 10 toneladas de emulsión catiónica súper estable (asfalto de imprimación), puesto en Aldea Protestante</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>miércoles 14 de octubre de 2026 – Hora nueve (09:00) Lugar de presentación de la oferta: Sede Comuna Aldea Protestan</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1585,7 +1579,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1603,14 +1601,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-c2f3a25cfb37fd38</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1618,14 +1616,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1635,34 +1633,30 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>017/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de UNA (1) MOTONIVELADORA, nueva, sin uso, cero km, con una potencia entre 220/240 HP, con opción a implementos, que será utilizada para el área del corralón municipal</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>14 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>$100.000,00. - (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1680,14 +1674,14 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-4c3b33859e596759</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1695,14 +1689,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1712,27 +1706,27 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>008/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
@@ -1753,66 +1747,62 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-a9af9f59c8c487c8</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>05/2026</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
           <t>28/09/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>MINISTERIO DE SALUD — GOBIERNO DE ENTRE RIOS</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Adquirir Sesenta Mil (60.000) Kilogramos de Leche Entera en Polvo Instantánea, Fortificada con Hierro, Zinc y Ácido Ascórbico</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>16/10/2026</t>
-        </is>
-      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>PESOS TRES MIL QUINIENTOS ($ 3.500,00)</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1830,60 +1820,64 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-04a917d50ccab2e3</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Municipalidad de Crespo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>5/2026</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
           <t>28/09/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>VILLAGUAY — MUNICIPALIDAD DE VILLAGUAY</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Contratación, ejecución, liquidación, pago y recepción de la obra destinada a la elaboración del Proyecto Ejecutivo, provisión de materiales, mano de obra, equipos, ejecución, ensayos, habilitación y puesta en servicio de la instalación de gas natural para la Planta Municipal de Elaboración de Mezcla Asfáltica en Caliente, ubicada en el Lote N.º 4 de la Chacra N.º 263 del Parque Industrial de Villaguay, Provincia de Entre Ríos. La contratación comprenderá una solución i ntegral bajo modalidad “llave en mano”, incluyendo todos los trabajos, provisiones, trámites, representaciones técnicas, insp</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>16/10/2026</t>
-        </is>
-      </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>16 de octubre del año 2026 a las 10:00 Horas, la que se realizara en la Ofici na de suministros de la Municipalidad de V</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>$ 50.000,00</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1898,19 +1892,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-55f1e5ca423a9262</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1920,12 +1914,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1933,20 +1927,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1956,7 +1954,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1976,7 +1974,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -1991,39 +1989,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>304/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2031,7 +2029,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2044,19 +2046,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2064,14 +2066,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2079,20 +2081,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2100,11 +2106,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2117,12 +2119,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2132,44 +2134,40 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>82/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>22/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2177,7 +2175,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2190,34 +2192,34 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2227,22 +2229,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2250,11 +2248,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2272,29 +2266,29 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-86cc9c230734c462</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2304,22 +2298,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2340,12 +2330,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-322a40f5e43af35d</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2355,19 +2345,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2377,22 +2367,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2402,7 +2388,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>$ 120.976,01</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -2417,12 +2403,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2432,19 +2418,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2454,22 +2440,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>Concurso de Precio N° 02/2025</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2490,19 +2472,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2512,33 +2494,29 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Vehículos</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>001/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2559,19 +2537,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-ca205f0874380f69</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2579,35 +2557,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta jurisdicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2628,19 +2606,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-24e9015ecceeff7f</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2648,14 +2626,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>INSTITUTO CARBÓ S.R.L</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2663,16 +2641,20 @@
           <t>Licitación</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2693,19 +2675,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-6aa57c7437a30ca3</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2713,14 +2695,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2730,18 +2712,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2762,12 +2744,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -2782,35 +2764,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2818,11 +2800,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2835,12 +2813,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
@@ -2857,33 +2835,33 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>233/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2904,12 +2882,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-f48b8e7889aac66c</t>
         </is>
       </c>
     </row>
@@ -2924,35 +2902,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>04/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2960,11 +2938,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K34" s="4" t="inlineStr"/>
       <c r="L34" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2977,12 +2951,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-2466cef612391e08</t>
         </is>
       </c>
     </row>
@@ -2997,35 +2971,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>232/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3046,289 +3020,17 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t>id-654eebef400f89cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>id-9a16884dd5a64a49</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>08/26</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="inlineStr">
-        <is>
-          <t>id-9ca2387eef6d6fc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-5a01c3fd726f10dc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O35"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3398,14 +3100,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P ARANA — MINISTERIO DE SALUD</t>
+          <t>PARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -874,14 +874,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -891,30 +891,34 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO ”</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+        </is>
+      </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -932,7 +936,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
@@ -964,12 +968,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C . P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -979,7 +983,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1005,14 +1009,14 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1020,14 +1024,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1037,12 +1041,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condiciones)</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1052,15 +1056,19 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
+          <t>13/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+        </is>
+      </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1078,7 +1086,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
@@ -1093,14 +1101,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1110,34 +1118,30 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1155,7 +1159,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
@@ -1170,14 +1174,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1187,34 +1191,30 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Gratuito</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1474,14 +1474,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1489,24 +1489,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>Hospital d e la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1516,7 +1512,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -1536,7 +1532,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
@@ -1551,29 +1547,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>304/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1583,7 +1579,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1591,7 +1587,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1624,9 +1624,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1636,27 +1636,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>82/2026</t>
+          <t>304/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1682,14 +1682,14 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1697,14 +1697,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1715,17 +1715,17 @@
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
@@ -1777,37 +1777,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>82/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
@@ -1843,14 +1843,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1858,14 +1858,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>09/2026</t>
-        </is>
-      </c>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1875,15 +1871,19 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1916,14 +1916,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1933,27 +1933,27 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1989,51 +1989,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2046,12 +2042,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2066,14 +2062,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2083,34 +2079,30 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2128,7 +2120,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -2143,49 +2135,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2200,12 +2192,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2220,14 +2212,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2237,22 +2229,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2260,7 +2252,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2273,12 +2269,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2288,9 +2284,9 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -2300,7 +2296,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2310,18 +2306,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2361,19 +2361,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2383,18 +2383,22 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2415,12 +2419,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2435,14 +2439,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2452,18 +2456,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2471,7 +2475,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2489,7 +2497,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2504,14 +2512,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2521,18 +2529,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2540,11 +2548,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2557,12 +2561,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2577,14 +2581,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2594,18 +2598,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2626,12 +2630,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2646,39 +2650,47 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
+          <t>Publicada 06/10/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2691,12 +2703,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2718,28 +2730,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2760,12 +2772,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2780,35 +2792,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2829,12 +2837,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2849,35 +2857,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2898,12 +2906,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2925,28 +2933,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2967,12 +2975,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -2994,28 +3002,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>04/26</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3036,19 +3044,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-2466cef612391e08</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3073,12 +3081,12 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>232/26</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -3110,7 +3118,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-5a01c3fd726f10dc</t>
+          <t>id-d3938e7b907594a8</t>
         </is>
       </c>
     </row>
@@ -3125,35 +3133,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>233/26</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3174,17 +3182,155 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>id-f48b8e7889aac66c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>04/26</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>id-2466cef612391e08</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>ENERSA</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O37"/>
+  <autoFilter ref="A1:O39"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3258,6 +3404,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1093,14 +1093,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1133,11 +1133,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1150,12 +1146,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1173,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1187,22 +1183,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1232,7 +1228,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1247,39 +1243,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>304/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1300,12 +1296,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
@@ -1327,32 +1323,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>82/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1360,11 +1356,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1377,12 +1369,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
@@ -1397,39 +1389,35 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>304/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1437,7 +1425,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1450,12 +1442,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1477,37 +1469,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>82/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -1523,12 +1515,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1535,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1558,10 +1550,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1571,19 +1567,15 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1596,12 +1588,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -1616,14 +1608,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1633,27 +1625,27 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -1674,7 +1666,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -1689,47 +1681,51 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1742,12 +1738,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1758,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1779,30 +1775,34 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -1835,49 +1835,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -1912,14 +1912,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1929,22 +1929,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1952,11 +1952,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1969,12 +1965,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -1984,9 +1980,9 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1996,7 +1992,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2006,22 +2002,18 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2031,7 +2023,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2051,7 +2043,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2061,19 +2053,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2083,22 +2075,18 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2119,12 +2107,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2139,14 +2127,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2156,18 +2144,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2175,11 +2163,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2197,7 +2181,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2219,28 +2203,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2261,12 +2245,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -2281,14 +2265,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2298,18 +2282,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2330,12 +2314,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -2350,35 +2334,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2386,11 +2370,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2403,19 +2383,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,35 +2403,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2472,12 +2452,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-d3938e7b907594a8</t>
         </is>
       </c>
     </row>
@@ -2492,31 +2472,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>233/26</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2537,12 +2521,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-f48b8e7889aac66c</t>
         </is>
       </c>
     </row>
@@ -2557,14 +2541,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2574,18 +2558,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>04/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2606,12 +2590,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-2466cef612391e08</t>
         </is>
       </c>
     </row>
@@ -2626,43 +2610,47 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
+          <t>Publicada 06/10/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2675,12 +2663,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2695,14 +2683,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2712,18 +2700,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2744,12 +2732,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2764,35 +2752,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>04-2026</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2813,12 +2797,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2833,35 +2817,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2882,155 +2866,17 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>04/26</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>id-2466cef612391e08</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>232/26</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>SERVICIO DE REACONDICIONAMIENTO Y REPARACIÓN EN SECTOR POSTERIOR DEL INMUEBLE ALQUILADO DEL JUZGADO DE PAZ DE SAN JAIME DE LA FRONTERA</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr"/>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t>id-5a01c3fd726f10dc</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O35"/>
+  <autoFilter ref="A1:O33"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3096,10 +2942,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P ARANA — MINISTERIO DE SALUD</t>
+          <t>PARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -874,14 +874,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -891,30 +891,34 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO ”</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+        </is>
+      </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -932,7 +936,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
@@ -964,12 +968,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C . P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -979,7 +983,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1005,14 +1009,14 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1020,14 +1024,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1037,12 +1041,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condiciones)</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1052,15 +1056,19 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026. - Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDA</t>
+          <t>13/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+        </is>
+      </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1078,7 +1086,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1108,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1110,27 +1118,27 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
@@ -1146,12 +1154,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1181,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1183,34 +1191,30 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1228,14 +1232,14 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1250,32 +1254,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>304/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>Hospital d e la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1283,7 +1283,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1296,12 +1300,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
@@ -1323,32 +1327,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>82/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1356,7 +1360,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1369,12 +1377,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1389,35 +1397,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
+          <t>CONCURSO DE PRECIOS</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>304/2026</t>
+        </is>
+      </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1425,11 +1437,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+      <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1442,19 +1450,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1462,14 +1470,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1477,32 +1485,32 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1520,7 +1528,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
@@ -1542,37 +1550,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>82/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -1588,12 +1596,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1623,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1623,32 +1631,32 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>05/2026</t>
-        </is>
-      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1666,7 +1674,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1681,51 +1689,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1738,12 +1742,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1758,14 +1762,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1775,34 +1779,30 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -1835,14 +1835,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1852,34 +1852,30 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1897,7 +1893,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -1912,47 +1908,51 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1980,19 +1980,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2002,18 +2002,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2043,7 +2047,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2053,19 +2057,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2075,18 +2079,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2094,7 +2102,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2112,7 +2124,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2122,19 +2134,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2144,18 +2156,22 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2176,12 +2192,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2196,43 +2212,47 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2245,12 +2265,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2265,14 +2285,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2282,18 +2302,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2314,12 +2334,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2334,35 +2354,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2383,19 +2403,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2403,35 +2423,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2452,19 +2472,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2472,35 +2492,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2521,19 +2541,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2541,35 +2561,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2590,19 +2610,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-2466cef612391e08</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2627,18 +2647,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2646,11 +2666,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2668,14 +2684,14 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2700,18 +2716,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2737,14 +2753,14 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2752,31 +2768,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2797,19 +2813,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2824,28 +2840,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2866,17 +2882,772 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>id-34c85bcdb9b1123f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>IAPV (Vivienda)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Publicada 08/10/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>id-75bfffae63b7eedc</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>IAPV (Vivienda)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Publicada 06/10/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>id-07ddb93a12c5a870</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>IAPV (Vivienda)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Concurso de Precio N° 02/2025</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Publicada 19/06/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>id-7c1bf02160a66f67</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>id-654eebef400f89cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>id-0691eb485d7548eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>10-2026</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>id-023b6b75e7014a9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>235/26</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>id-d3938e7b907594a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>233/26</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>id-f48b8e7889aac66c</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>04/26</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>id-2466cef612391e08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O33"/>
+  <autoFilter ref="A1:O44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -2942,6 +3713,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -3304,7 +3304,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3319,28 +3319,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-d3938e7b907594a8</t>
         </is>
       </c>
     </row>
@@ -3388,28 +3388,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>233/26</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-f48b8e7889aac66c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>04/26</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -3504,150 +3504,12 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>233/26</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
-          <t>id-f48b8e7889aac66c</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>04/26</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O44" s="4" t="inlineStr">
-        <is>
           <t>id-2466cef612391e08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O44"/>
+  <autoFilter ref="A1:O42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3731,10 +3593,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -866,7 +866,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -874,14 +874,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>32/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO ”</t>
+          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>08 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -914,11 +914,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
-        </is>
-      </c>
+      <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -936,14 +932,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-0ace7de8f16d3baf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -951,14 +947,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -968,27 +964,27 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>33/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>08 de octubre de 2026 Hora: 11:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
@@ -1009,7 +1005,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-fe71ac2aaf71b8d8</t>
         </is>
       </c>
     </row>
@@ -1024,14 +1020,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1041,22 +1037,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condiciones)</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO ”</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10:00 HS</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1066,7 +1062,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -1086,14 +1082,14 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-1a2561509308b1b6</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1101,14 +1097,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1118,27 +1114,27 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>34/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>09 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
@@ -1159,14 +1155,14 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-b147fbd9d3081bfc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1174,14 +1170,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1191,12 +1187,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condiciones)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1206,15 +1202,19 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>13/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+        </is>
+      </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
@@ -1247,14 +1247,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1264,34 +1264,30 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1309,7 +1305,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1320,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1341,34 +1337,30 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1386,7 +1378,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
@@ -1401,14 +1393,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1418,27 +1410,27 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1454,12 +1446,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1494,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Hospital d e la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1547,7 +1539,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1725,7 +1717,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entr e Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1770,7 +1762,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1843,7 +1835,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
@@ -1916,7 +1908,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1989,7 +1981,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -2062,7 +2054,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
@@ -2135,7 +2127,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
@@ -2289,7 +2281,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -2366,7 +2358,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -2431,7 +2423,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2439,14 +2431,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2456,18 +2448,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2475,11 +2467,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2497,7 +2485,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2502,12 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2529,18 +2517,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2548,7 +2536,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2566,7 +2558,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2581,14 +2573,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2598,12 +2590,12 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2635,7 +2627,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2650,14 +2642,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2667,18 +2659,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2686,11 +2678,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2703,12 +2691,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2745,13 +2733,13 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2759,7 +2747,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2777,7 +2769,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2792,31 +2784,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2837,12 +2833,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2857,9 +2853,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2869,17 +2865,13 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2911,7 +2903,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2926,35 +2918,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2975,12 +2967,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2987,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -3007,17 +2999,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -3049,14 +3041,14 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3064,35 +3056,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3113,19 +3105,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3133,7 +3125,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -3150,12 +3142,12 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>236/26</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -3187,14 +3179,14 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
+          <t>id-d0f81989a1411fa1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3202,7 +3194,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -3214,17 +3206,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>04/26</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -3256,7 +3248,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-2466cef612391e08</t>
+          <t>id-d3938e7b907594a8</t>
         </is>
       </c>
     </row>
@@ -3273,33 +3265,33 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>233/26</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3320,17 +3312,86 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>id-f48b8e7889aac66c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>ENERSA</t>
         </is>
       </c>
-      <c r="O39" s="4" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3408,6 +3469,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1320,29 +1320,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>304/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1360,11 +1360,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1377,19 +1373,19 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1404,32 +1400,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>304/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1437,7 +1429,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1450,19 +1446,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1470,35 +1466,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
+          <t>LICITACIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>82/2026</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1506,11 +1506,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1523,12 +1519,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
@@ -1543,39 +1539,35 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>82/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1583,7 +1575,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1596,12 +1592,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1616,14 +1612,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1631,10 +1627,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1644,19 +1644,15 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1674,7 +1670,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1692,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1706,12 +1702,12 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1721,7 +1717,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1747,7 +1743,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1758,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1779,27 +1775,27 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -1820,7 +1816,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -1842,22 +1838,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1867,15 +1863,19 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1908,49 +1908,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -1985,14 +1985,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2002,22 +2002,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2102,11 +2102,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2119,12 +2115,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2134,9 +2130,9 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2146,7 +2142,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2156,22 +2152,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2179,7 +2171,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2192,12 +2188,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2212,14 +2208,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2229,18 +2225,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2248,11 +2244,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2270,7 +2262,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2285,14 +2277,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2302,12 +2294,12 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -2339,14 +2331,14 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2354,14 +2346,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2371,18 +2363,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2403,12 +2395,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2440,18 +2432,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2477,7 +2469,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2509,18 +2501,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2546,7 +2538,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -2578,18 +2570,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2615,7 +2607,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2647,18 +2639,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2684,7 +2676,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2714,20 +2706,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>06/2025</t>
-        </is>
-      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2753,7 +2741,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -2783,16 +2771,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2818,7 +2810,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -2850,18 +2842,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2887,14 +2879,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2919,18 +2911,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2956,7 +2948,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2993,13 +2985,13 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3025,7 +3017,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3040,35 +3032,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3089,12 +3077,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -3109,9 +3097,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3121,13 +3109,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr"/>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -3159,7 +3151,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3174,29 +3166,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -3223,19 +3215,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3243,35 +3235,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3292,19 +3284,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-d3938e7b907594a8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3329,12 +3321,12 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>233/26</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -3366,7 +3358,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-f48b8e7889aac66c</t>
         </is>
       </c>
     </row>
@@ -3393,17 +3385,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>04/26</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -3435,81 +3427,12 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>04/26</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
           <t>id-2466cef612391e08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3591,8 +3514,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1539,29 +1539,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>304/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1579,11 +1579,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1596,19 +1592,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1623,32 +1619,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>304/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entr e Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1656,7 +1648,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1669,19 +1665,19 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1689,35 +1685,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>LICITACIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>82/2026</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entr e Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1725,11 +1725,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1742,12 +1738,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
@@ -1762,39 +1758,35 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>82/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1802,7 +1794,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1815,12 +1811,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1835,14 +1831,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1850,10 +1846,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1863,19 +1863,15 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1893,7 +1889,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1911,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1925,12 +1921,12 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1940,7 +1936,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1961,12 +1957,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -1981,14 +1977,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1998,27 +1994,27 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr"/>
@@ -2034,12 +2030,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2057,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2086,15 +2082,19 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2127,49 +2127,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2204,14 +2204,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2221,22 +2221,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2321,11 +2321,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2338,34 +2334,34 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2375,22 +2371,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2411,19 +2403,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2431,14 +2423,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2448,18 +2440,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2467,7 +2459,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2485,7 +2481,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2500,14 +2496,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2517,18 +2513,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2536,11 +2532,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2558,7 +2550,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2573,14 +2565,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2590,12 +2582,12 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2627,7 +2619,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2642,14 +2634,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2659,18 +2651,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2678,7 +2670,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2691,12 +2687,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2733,13 +2729,13 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2747,11 +2743,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2769,7 +2761,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2784,35 +2776,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2833,12 +2821,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2853,9 +2841,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2865,13 +2853,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2903,7 +2895,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2918,35 +2910,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2967,12 +2959,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -2999,17 +2991,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -3041,14 +3033,14 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3063,28 +3055,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>236/26</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3105,19 +3097,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-d0f81989a1411fa1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3142,12 +3134,12 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>236/26</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -3179,14 +3171,14 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-d0f81989a1411fa1</t>
+          <t>id-d3938e7b907594a8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3211,12 +3203,12 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>233/26</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -3248,7 +3240,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-f48b8e7889aac66c</t>
         </is>
       </c>
     </row>
@@ -3263,35 +3255,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3312,86 +3304,17 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O39"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3469,8 +3392,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,17 +62,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E6D9F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -653,37 +653,37 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>016/2026</t>
+          <t>86/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
+          <t>ADQUISICION DE CAL VIVA AEREA</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>01-10-2026 08:00</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -691,11 +691,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
-        </is>
-      </c>
+      <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -708,12 +704,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-53f1430f94acb0b0</t>
+          <t>id-ee4153887a6e1e8d</t>
         </is>
       </c>
     </row>
@@ -728,47 +724,51 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE SALUD</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Licitación Publica</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>016/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -786,7 +786,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-3312d89e1a3e2e53</t>
+          <t>id-53f1430f94acb0b0</t>
         </is>
       </c>
     </row>
@@ -801,44 +801,44 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>PARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>31/2026</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>07 de octubre de 2026 Hora: 10:00</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
@@ -859,14 +859,14 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-76d9566cb30a6df5</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -874,14 +874,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO ”</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -914,11 +914,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
-        </is>
-      </c>
+      <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -936,14 +932,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -951,14 +947,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -968,27 +964,27 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>32/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>08 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
@@ -1009,14 +1005,14 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-0ace7de8f16d3baf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1024,14 +1020,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1041,22 +1037,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>33/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condiciones)</t>
+          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10:00 HS</t>
+          <t>08 de octubre de 2026 Hora: 11:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1064,11 +1060,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
-        </is>
-      </c>
+      <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1086,14 +1078,14 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-1a2561509308b1b6</t>
+          <t>id-fe71ac2aaf71b8d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1101,14 +1093,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1118,30 +1110,34 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1159,14 +1155,14 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1174,14 +1170,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1191,27 +1187,27 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>34/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“ Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de B ases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>09 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1232,7 +1228,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-b147fbd9d3081bfc</t>
         </is>
       </c>
     </row>
@@ -1247,14 +1243,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1262,20 +1258,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>11/2026</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Hospital d e la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>13/10/2026 HORA: 10: 00 HS</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
@@ -1320,44 +1320,44 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>304/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -1373,19 +1373,19 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1393,14 +1393,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1408,32 +1408,32 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>13/2026</t>
+        </is>
+      </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
@@ -1466,44 +1466,44 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>82/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1539,14 +1539,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1554,20 +1554,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>008/2026</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales, Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1575,11 +1579,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1597,14 +1597,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-a9af9f59c8c487c8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1627,32 +1627,32 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1670,14 +1670,14 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1700,32 +1700,32 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>09/2026</t>
-        </is>
-      </c>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1743,14 +1743,14 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1758,44 +1758,44 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>308/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>CONTRATACION DE SERVICIO DE ILUMINACION, PANTALLA LED Y SONIDO</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>23-09-2026 10:30</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-e39cbe830cc7226a</t>
         </is>
       </c>
     </row>
@@ -1831,49 +1831,45 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>5/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1888,12 +1884,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1908,14 +1904,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1925,34 +1921,30 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1970,7 +1962,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1985,14 +1977,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2002,34 +1994,30 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2042,12 +2030,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2062,14 +2050,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2079,27 +2067,27 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2115,12 +2103,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -2130,50 +2118,54 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2188,12 +2180,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2203,19 +2195,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2225,18 +2217,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2244,7 +2240,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2272,19 +2272,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2294,18 +2294,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2313,7 +2317,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2331,29 +2339,29 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2363,18 +2371,22 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2395,19 +2407,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2415,14 +2427,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2432,18 +2444,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a c ontinuación se detalla y</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2464,19 +2476,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2484,14 +2496,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2501,18 +2513,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2520,7 +2532,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2533,19 +2549,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2555,12 +2571,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2570,18 +2586,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2602,19 +2618,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2622,14 +2638,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2639,18 +2655,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2671,12 +2687,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2707,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2706,16 +2722,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>03/26</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2741,7 +2761,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2776,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2773,18 +2793,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2810,7 +2830,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2845,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2842,18 +2862,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2879,14 +2899,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2894,7 +2914,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2911,18 +2931,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2948,14 +2968,14 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2963,7 +2983,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2980,18 +3000,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3017,14 +3037,14 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3032,31 +3052,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3077,19 +3097,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3097,35 +3117,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3146,19 +3166,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3166,35 +3186,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3215,19 +3235,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3237,33 +3257,33 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3284,12 +3304,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3306,33 +3326,33 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3353,12 +3373,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3373,35 +3393,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>04/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Edif. Tribunales – Chajarí, departamento de Federación. Obra “Reparaciones generales de baños e instalación eléctrica – 2° piso”</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3422,17 +3438,500 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>id-654eebef400f89cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>id-9a16884dd5a64a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>id-0691eb485d7548eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>10-2026</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>id-023b6b75e7014a9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>id-2466cef612391e08</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>236/26</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>id-d0f81989a1411fa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>235/26</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>id-d3938e7b907594a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>233/26</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>id-f48b8e7889aac66c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O48"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3514,6 +4013,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO ”</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“ Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de B ases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condiciones)</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10:00 HS</t>
+          <t>13/10/2026 HORA: 10: 00 HS</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1466,14 +1466,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1481,20 +1481,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>008/2026</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales, Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1502,11 +1506,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1524,14 +1524,14 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-a9af9f59c8c487c8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1546,32 +1546,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>304/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1579,7 +1575,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1592,19 +1592,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1619,28 +1619,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>CONCURSO DE PRECIOS</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>304/2026</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entr e Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1648,11 +1652,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1665,19 +1665,19 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1685,39 +1685,35 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>82/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1725,7 +1721,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
@@ -1758,35 +1758,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
+          <t>LICITACIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>82/2026</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1794,11 +1798,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+      <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
@@ -1831,14 +1831,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1846,14 +1846,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1863,15 +1859,19 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1977,14 +1977,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1994,27 +1994,27 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr"/>
@@ -2030,12 +2030,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2057,22 +2057,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2082,19 +2082,15 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2107,12 +2103,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -2127,49 +2123,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2184,12 +2180,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2204,14 +2200,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2221,22 +2217,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2246,7 +2242,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -2266,7 +2262,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2284,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2298,12 +2294,12 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2313,7 +2309,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2321,7 +2317,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2334,34 +2334,34 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2371,18 +2371,22 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2403,19 +2407,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,14 +2427,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2440,18 +2444,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a c ontinuación se detalla y</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2459,11 +2463,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
@@ -2496,14 +2496,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2513,18 +2513,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2532,7 +2532,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2550,7 +2554,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2565,14 +2569,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2582,12 +2586,12 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2619,7 +2623,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2634,14 +2638,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2651,18 +2655,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2670,11 +2674,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2687,12 +2687,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2729,13 +2729,13 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2743,7 +2743,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2761,7 +2765,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2776,31 +2780,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2821,12 +2829,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2841,9 +2849,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2853,17 +2861,13 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2895,7 +2899,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2910,35 +2914,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2959,12 +2963,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2995,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -3033,14 +3037,14 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3055,28 +3059,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>236/26</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3097,19 +3101,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-d0f81989a1411fa1</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3134,12 +3138,12 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>240/26</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -3171,14 +3175,14 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3203,12 +3207,12 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>236/26</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -3240,14 +3244,14 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
+          <t>id-d0f81989a1411fa1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3255,35 +3259,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3304,17 +3308,86 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>id-d3938e7b907594a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>ENERSA</t>
         </is>
       </c>
-      <c r="O39" s="4" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3392,6 +3465,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -2699,7 +2699,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2707,14 +2707,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2724,18 +2724,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2756,19 +2756,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2776,35 +2776,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2825,19 +2825,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2845,35 +2845,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>240/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2894,19 +2894,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2914,35 +2914,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>236/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2963,19 +2963,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-d0f81989a1411fa1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2983,35 +2983,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-d3938e7b907594a8</t>
         </is>
       </c>
     </row>
@@ -3067,16 +3067,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>03/26</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3102,7 +3106,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -3134,18 +3138,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3171,7 +3175,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -3203,18 +3207,18 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3240,14 +3244,14 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3272,18 +3276,18 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3309,14 +3313,14 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3341,18 +3345,18 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3378,14 +3382,14 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3393,31 +3397,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3438,19 +3442,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3465,28 +3469,28 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3507,19 +3511,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3527,35 +3531,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -3576,12 +3580,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -3596,14 +3600,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3613,18 +3617,18 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3645,12 +3649,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3665,35 +3669,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3714,19 +3718,19 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3734,35 +3738,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>236/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3783,19 +3783,19 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>id-d0f81989a1411fa1</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3803,35 +3803,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3872,35 +3872,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>233/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Reemplazo, provisión e instalación de las barreras vehiculares automáticas en el Edificio Central de Tribunales, de Paraná (sito Laprida N°250).</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>id-f48b8e7889aac66c</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,11 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -101,6 +106,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1012,7 +1018,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1027,7 +1033,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1037,12 +1043,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>34/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
+          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1052,7 +1058,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>09 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1060,11 +1066,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
-        </is>
-      </c>
+      <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1082,14 +1084,14 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-b147fbd9d3081bfc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1104,7 +1106,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1114,12 +1116,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>34/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“ Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de B ases, Condiciones Particulares y demás documentación</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1129,7 +1131,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>09 de octubre de 2026 Hora: 10:00</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1137,7 +1139,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1155,7 +1161,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-b147fbd9d3081bfc</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1494,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales, Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1823,7 +1829,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1831,14 +1837,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1846,20 +1852,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>11/26</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO -DEPARTAMENTO GUALEGUAY.”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1869,7 +1879,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1889,14 +1899,14 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-86cc9c230734c462</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1911,7 +1921,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1921,27 +1931,27 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -1957,12 +1967,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-322a40f5e43af35d</t>
         </is>
       </c>
     </row>
@@ -1977,14 +1987,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1992,14 +2002,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>09/2026</t>
-        </is>
-      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2009,15 +2015,19 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2030,12 +2040,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -2050,14 +2060,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2067,27 +2077,27 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2108,7 +2118,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -2123,51 +2133,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2180,12 +2186,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2200,14 +2206,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2217,34 +2223,30 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2262,7 +2264,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -2277,49 +2279,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2334,12 +2336,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2356,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2371,22 +2373,22 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2394,7 +2396,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2407,34 +2413,34 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2444,18 +2450,22 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a c ontinuación se detalla y</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2463,7 +2473,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2481,7 +2495,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2491,9 +2505,9 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -2503,7 +2517,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2513,18 +2527,22 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2532,11 +2550,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2549,19 +2563,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2569,14 +2583,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2586,18 +2600,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta jurisdicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2623,14 +2637,14 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-24e9015ecceeff7f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2638,29 +2652,25 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>INSTITUTO CARBÓ S.R.L</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>01/2026</t>
-        </is>
-      </c>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -2692,14 +2702,14 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-6aa57c7437a30ca3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2714,7 +2724,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2724,18 +2734,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2743,11 +2753,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2760,12 +2766,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
@@ -2780,14 +2786,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2797,18 +2803,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2816,7 +2822,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2829,12 +2839,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2856,24 +2866,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2894,12 +2908,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2914,35 +2928,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2963,12 +2977,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2997,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3000,18 +3014,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3019,7 +3033,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -3032,12 +3050,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3052,35 +3070,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3101,19 +3119,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3121,35 +3139,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>240/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3170,19 +3184,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3190,35 +3204,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>236/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3239,19 +3253,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-d0f81989a1411fa1</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3266,28 +3280,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3308,12 +3322,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -3328,35 +3342,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3377,17 +3391,224 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>id-023b6b75e7014a9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>240/26</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>id-ba80195eeddbd2bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>236/26</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>id-d0f81989a1411fa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>ENERSA</t>
         </is>
       </c>
-      <c r="O40" s="4" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O43"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3467,6 +3688,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1846,32 +1846,32 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>05/2026</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -1904,47 +1904,51 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1957,12 +1961,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1977,14 +1981,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1994,30 +1998,34 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2030,12 +2038,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2050,14 +2058,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2067,30 +2075,34 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2108,7 +2120,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2123,51 +2135,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2180,34 +2188,34 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2217,22 +2225,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
+          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a c ontinuación se detalla y</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2240,11 +2244,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
@@ -2272,9 +2272,9 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2294,22 +2294,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2319,7 +2315,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2339,7 +2335,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2349,19 +2345,19 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2371,22 +2367,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2407,19 +2399,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2427,14 +2419,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2444,12 +2436,12 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a c ontinuación se detalla y</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -2481,7 +2473,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2495,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2513,18 +2505,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2532,11 +2524,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2549,12 +2537,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -2569,35 +2557,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2618,19 +2606,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2638,35 +2626,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>240/26</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2687,19 +2675,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2714,28 +2702,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>236/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2756,19 +2744,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-d0f81989a1411fa1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2783,28 +2771,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2825,19 +2813,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-d3938e7b907594a8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2845,35 +2833,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>240/26</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2894,19 +2882,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2914,35 +2902,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>236/26</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2963,19 +2951,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-d0f81989a1411fa1</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2983,35 +2971,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3032,12 +3020,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -3069,18 +3057,18 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3106,7 +3094,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -3138,18 +3126,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3175,7 +3163,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -3205,20 +3193,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>01/2026</t>
-        </is>
-      </c>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3244,7 +3228,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -3276,18 +3260,18 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3313,7 +3297,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -3345,18 +3329,18 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3382,14 +3366,14 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3412,16 +3396,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3447,14 +3435,14 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3479,18 +3467,18 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3516,14 +3504,14 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3531,35 +3519,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>03/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -3580,12 +3564,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -3607,28 +3591,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3649,12 +3633,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3669,35 +3653,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3718,220 +3702,17 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="O46" s="4" t="inlineStr">
-        <is>
-          <t>id-654eebef400f89cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="O47" s="4" t="inlineStr">
-        <is>
-          <t>id-9a16884dd5a64a49</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O48" s="4" t="inlineStr">
-        <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O48"/>
+  <autoFilter ref="A1:O45"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -4021,12 +3802,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -726,7 +726,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -734,29 +734,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE SALUD</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Licitación Publica</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -766,15 +766,19 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>06/10/2026 HORA: 11:00 HS</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -792,7 +796,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-3312d89e1a3e2e53</t>
+          <t>id-65d18d99bf0b2c6c</t>
         </is>
       </c>
     </row>
@@ -814,37 +818,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>PARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>31/2026</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>07 de octubre de 2026 Hora: 10:00</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
@@ -865,14 +869,14 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-76d9566cb30a6df5</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -880,9 +884,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -897,22 +901,22 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>32/2026</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 10:00</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -938,7 +942,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-0ace7de8f16d3baf</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
@@ -953,9 +957,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -970,12 +974,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>33/2026</t>
+          <t>32/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -985,7 +989,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 11:00</t>
+          <t>08 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1011,7 +1015,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-fe71ac2aaf71b8d8</t>
+          <t>id-0ace7de8f16d3baf</t>
         </is>
       </c>
     </row>
@@ -1026,14 +1030,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1043,22 +1047,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>34/2026</t>
+          <t>33/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>09 de octubre de 2026 Hora: 10:00</t>
+          <t>08 de octubre de 2026 Hora: 11:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1084,14 +1088,14 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-b147fbd9d3081bfc</t>
+          <t>id-fe71ac2aaf71b8d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1116,12 +1120,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>34/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
+          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1131,7 +1135,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>09 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1139,11 +1143,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
-        </is>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-b147fbd9d3081bfc</t>
         </is>
       </c>
     </row>
@@ -1176,14 +1176,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10: 00 HS</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-1a2561509308b1b6</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1253,14 +1253,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1285,15 +1285,19 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>13/10/2026 HORA: 10: 00 HS</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+        </is>
+      </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1311,7 +1315,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1330,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1343,12 +1347,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1358,7 +1362,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1384,7 +1388,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1403,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1416,12 +1420,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1431,7 +1435,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1457,14 +1461,14 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1472,14 +1476,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1489,27 +1493,27 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>008/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -1530,14 +1534,14 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-a9af9f59c8c487c8</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1545,14 +1549,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1560,20 +1564,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>008/2026</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1581,11 +1589,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1603,14 +1607,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-a9af9f59c8c487c8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1625,32 +1629,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>304/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1658,7 +1658,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1671,19 +1675,19 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1698,28 +1702,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>CONCURSO DE PRECIOS</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>304/2026</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1727,11 +1735,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1744,19 +1748,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1764,39 +1768,35 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>82/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1804,7 +1804,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1817,19 +1821,19 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1837,39 +1841,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>82/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO -DEPARTAMENTO GUALEGUAY.”</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1877,11 +1881,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-86cc9c230734c462</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
@@ -1914,14 +1914,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>11/26</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1954,7 +1954,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1967,19 +1971,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-322a40f5e43af35d</t>
+          <t>id-86cc9c230734c462</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1989,12 +1993,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2002,20 +2006,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>11/2026</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2023,11 +2031,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2040,12 +2044,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-322a40f5e43af35d</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2066,12 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2077,27 +2081,27 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2118,7 +2122,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -2135,45 +2139,49 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2186,12 +2194,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2206,14 +2214,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2223,30 +2231,34 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2264,7 +2276,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2281,47 +2293,47 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2336,12 +2348,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2368,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2373,22 +2385,22 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2396,11 +2408,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2413,34 +2421,34 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2450,22 +2458,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>001/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2473,11 +2477,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2495,29 +2495,29 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-ca205f0874380f69</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2527,22 +2527,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2563,12 +2559,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-24e9015ecceeff7f</t>
         </is>
       </c>
     </row>
@@ -2583,35 +2579,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>INSTITUTO CARBÓ S.R.L</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta jurisdicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2637,14 +2629,14 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-24e9015ecceeff7f</t>
+          <t>id-6aa57c7437a30ca3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2659,18 +2651,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>INSTITUTO CARBÓ S.R.L</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>08/26</t>
+        </is>
+      </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
+          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -2702,14 +2698,14 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-6aa57c7437a30ca3</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2717,14 +2713,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2734,18 +2730,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2753,7 +2749,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2803,18 +2803,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2822,11 +2822,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2844,7 +2840,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2859,14 +2855,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2876,12 +2872,12 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2913,7 +2909,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2928,14 +2924,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2945,18 +2941,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2964,7 +2960,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3019,13 +3019,13 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3033,11 +3033,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -3055,7 +3051,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3070,35 +3066,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3119,12 +3111,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -3139,9 +3131,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3151,13 +3143,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr"/>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -3189,14 +3185,14 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3204,35 +3200,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3253,19 +3249,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-9ca2387eef6d6fc1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3273,35 +3269,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>240/26</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3322,12 +3318,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
@@ -3344,33 +3340,33 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3391,224 +3387,17 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>240/26</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>id-ba80195eeddbd2bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>236/26</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>id-d0f81989a1411fa1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O43"/>
+  <autoFilter ref="A1:O40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3688,12 +3477,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,11 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -101,6 +106,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -793,7 +799,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -801,29 +807,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE SALUD</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Licitación Publica</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -833,15 +839,19 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>06/10/2026 HORA: 11:00 HS</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -859,7 +869,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-3312d89e1a3e2e53</t>
+          <t>id-65d18d99bf0b2c6c</t>
         </is>
       </c>
     </row>
@@ -881,37 +891,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>PARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>31/2026</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>07 de octubre de 2026 Hora: 10:00</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -932,14 +942,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-76d9566cb30a6df5</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -947,9 +957,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -964,22 +974,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>32/2026</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 10:00</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1005,7 +1015,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-0ace7de8f16d3baf</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
@@ -1020,9 +1030,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1037,12 +1047,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>33/2026</t>
+          <t>32/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1052,7 +1062,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 11:00</t>
+          <t>08 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1078,14 +1088,14 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-fe71ac2aaf71b8d8</t>
+          <t>id-0ace7de8f16d3baf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1093,14 +1103,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1110,22 +1120,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>33/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
+          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>08 de octubre de 2026 Hora: 11:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1133,11 +1143,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
-        </is>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1155,7 +1161,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-fe71ac2aaf71b8d8</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1183,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1192,7 +1198,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“ Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de B ases, Condiciones Particulares y demás documentación</t>
+          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1243,14 +1249,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1260,22 +1266,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10: 00 HS</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1285,7 +1291,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1305,14 +1311,14 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-1a2561509308b1b6</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1320,14 +1326,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1342,7 +1348,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1352,15 +1358,19 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>13/10/2026 HORA: 10: 00 HS</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+        </is>
+      </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1378,7 +1388,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1420,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1425,7 +1435,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1451,7 +1461,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1493,12 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1498,7 +1508,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1524,14 +1534,14 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1539,14 +1549,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1556,27 +1566,27 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>008/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales, Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -1597,14 +1607,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-a9af9f59c8c487c8</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1612,14 +1622,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1627,20 +1637,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>008/2026</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1648,11 +1662,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1670,7 +1680,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-a9af9f59c8c487c8</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1702,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1703,17 +1713,17 @@
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1743,14 +1753,14 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1765,32 +1775,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>308/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE ILUMINACION, PANTALLA LED Y SONIDO</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>23-09-2026 10:30</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1798,7 +1804,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1811,19 +1821,19 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-e39cbe830cc7226a</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1831,14 +1841,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1848,30 +1858,34 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>11/26</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1889,14 +1903,14 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-86cc9c230734c462</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1904,51 +1918,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1961,12 +1971,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-322a40f5e43af35d</t>
         </is>
       </c>
     </row>
@@ -1981,14 +1991,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1998,34 +2008,30 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2043,7 +2049,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
@@ -2058,49 +2064,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2115,12 +2121,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2135,14 +2141,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2152,22 +2158,22 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2175,7 +2181,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2188,34 +2198,34 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2225,18 +2235,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>de asfalto 70- 16 destinado a la producción de pavimento de la Planta Asfáltica, y que a c ontinuación se detalla y</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2244,7 +2258,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2262,7 +2280,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2272,9 +2290,9 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2284,7 +2302,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2294,18 +2312,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2313,11 +2335,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2330,19 +2348,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2350,14 +2368,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2367,18 +2385,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>001/26</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2404,14 +2422,14 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-ca205f0874380f69</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2419,14 +2437,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2436,18 +2454,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2473,14 +2491,14 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-24e9015ecceeff7f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2488,35 +2506,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>INSTITUTO CARBÓ S.R.L</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2537,19 +2551,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-6aa57c7437a30ca3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2557,35 +2571,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2606,19 +2620,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-023b6b75e7014a9c</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2633,28 +2647,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>240/26</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2662,7 +2676,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2675,19 +2693,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2695,35 +2713,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>236/26</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Provisión y envío de materiales de pinturería para el Taller de Mantenimiento del Edificio Tribunales localidad Concordia.</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2744,19 +2762,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-d0f81989a1411fa1</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2764,35 +2782,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Contratación de servicio para puesta en marcha de Grupo Electrógeno 30KVA, ubicado en el Edificio Tribunales de C. del Uruguay, calle San Martín Nº665.</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2813,12 +2831,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-d3938e7b907594a8</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -3711,8 +3729,146 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>08/26</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>id-9ca2387eef6d6fc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>240/26</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>id-ba80195eeddbd2bd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O45"/>
+  <autoFilter ref="A1:O47"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3802,6 +3958,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2774,7 +2774,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2782,14 +2782,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2799,18 +2799,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2868,18 +2868,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2937,18 +2937,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -3006,18 +3006,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -3075,18 +3075,18 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -3142,20 +3142,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>06/2025</t>
-        </is>
-      </c>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3181,7 +3177,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -3211,16 +3207,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -3278,18 +3278,18 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3315,14 +3315,14 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3347,18 +3347,18 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3421,13 +3421,13 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3468,35 +3468,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3517,12 +3513,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -3537,9 +3533,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3549,13 +3545,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr"/>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3602,29 +3602,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -3651,19 +3651,19 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3671,35 +3671,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3720,19 +3720,19 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-9ca2387eef6d6fc1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3752,17 +3752,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>240/26</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -3794,81 +3794,12 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>id-9ca2387eef6d6fc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>240/26</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O47" s="4" t="inlineStr">
-        <is>
           <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O47"/>
+  <autoFilter ref="A1:O46"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3960,8 +3891,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -2774,7 +2774,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2782,35 +2782,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>03/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2831,19 +2827,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2858,28 +2854,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2900,19 +2896,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2920,35 +2916,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2969,19 +2965,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2989,14 +2985,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3006,18 +3002,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3038,19 +3034,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-9ca2387eef6d6fc1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3058,35 +3054,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>240/26</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3107,12 +3103,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
@@ -3142,16 +3138,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>03/26</t>
+        </is>
+      </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -3209,18 +3209,18 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -3278,18 +3278,18 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3315,14 +3315,14 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3347,18 +3347,18 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3384,14 +3384,14 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3416,18 +3416,18 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3453,14 +3453,14 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3468,31 +3468,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3513,19 +3513,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3540,28 +3540,28 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -3582,19 +3582,19 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3602,35 +3602,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3651,19 +3651,19 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3671,14 +3671,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3688,18 +3688,18 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3720,19 +3720,19 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>id-9ca2387eef6d6fc1</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3740,35 +3740,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>240/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1541,7 +1541,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1549,14 +1549,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
+          <t>MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1564,14 +1564,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>008/2026</t>
-        </is>
-      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
+          <t>“ADQUISICIÓN DE MATERIALES ELÉCTRICOS PARA EJECUCIÓN DEL PROYECTO DE RECONVERSIÓN Y OPTIMIZACIÓN DEL ALUMBRADO PÚBLICO DE LA CIUDAD DE COLÓN”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1581,7 +1577,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
+          <t>14 de OCTUBRE de 2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1589,7 +1585,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1607,14 +1607,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-a9af9f59c8c487c8</t>
+          <t>id-9e122d52de12ffef</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1622,14 +1622,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1637,20 +1637,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>017/2026</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de UNA (1) MOTONIVELADORA, nueva, sin uso, cero km, con una potencia entre 220/240 HP, con opción a implementos, que será utilizada para el área del corralón municipal</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>14 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1660,7 +1664,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>$100.000,00. - (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1680,14 +1684,14 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-4c3b33859e596759</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1695,39 +1699,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>304/2026</t>
+          <t>008/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1748,19 +1752,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-a9af9f59c8c487c8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1768,14 +1772,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
+          <t>MINISTERIO DE SALUD — GOBIERNO DE ENTRE RIOS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1783,20 +1787,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>18/26</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>Adquirir Sesenta Mil (60.000) Kilogramos de Leche Entera en Polvo Instantánea, Fortificada con Hierro, Zinc y Ácido Ascórbico</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1806,7 +1814,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>PESOS TRES MIL QUINIENTOS ($ 3.500,00)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1826,14 +1834,14 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-04a917d50ccab2e3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1841,39 +1849,35 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>VILLAGUAY — MUNICIPALIDAD DE VILLAGUAY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>82/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>Contratación, ejecución, liquidación, pago y recepción de la obra destinada a la elaboración del Proyecto Ejecutivo, provisión de materiales, mano de obra, equipos, ejecución, ensayos, habilitación y puesta en servicio de la instalación de gas natural para la Planta Municipal de Elaboración de Mezcla Asfáltica en Caliente, ubicada en el Lote N.º 4 de la Chacra N.º 263 del Parque Industrial de Villaguay, Provincia de Entre Ríos. La contratación comprenderá una solución integral bajo modalidad “llave en mano”, incluyendo todos los trabajos, provisiones, trámites, representaciones técnicas, inspe</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>16 de octubre del año 2026 a las 10:00 Horas, la que se realizara en la Ofic ina de suministros de la Municipalidad de V</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1881,7 +1885,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>$ 50.000,00</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1894,19 +1902,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-55f1e5ca423a9262</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1914,14 +1922,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1929,24 +1937,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>11/26</t>
-        </is>
-      </c>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
+          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1956,7 +1960,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1976,14 +1980,14 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-86cc9c230734c462</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1991,39 +1995,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>304/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2044,19 +2048,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-322a40f5e43af35d</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2064,14 +2068,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2079,32 +2083,32 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>05/2026</t>
-        </is>
-      </c>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2122,7 +2126,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
@@ -2137,51 +2141,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>82/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2194,19 +2194,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2214,14 +2214,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>11/26</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -2276,14 +2276,14 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-86cc9c230734c462</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2308,22 +2308,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2331,11 +2331,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2348,12 +2344,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-322a40f5e43af35d</t>
         </is>
       </c>
     </row>
@@ -2368,14 +2364,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2385,27 +2381,27 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -2421,63 +2417,71 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-61e8747a99305fe9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>001/26</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
+          <t>28/9/2026 – 10:00 horas Ver acta</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2490,34 +2494,34 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-ca205f0874380f69</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2527,18 +2531,22 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2546,7 +2554,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2564,46 +2576,54 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-24e9015ecceeff7f</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>INSTITUTO CARBÓ S.R.L</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2611,7 +2631,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2629,29 +2653,29 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-6aa57c7437a30ca3</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2661,18 +2685,22 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2693,19 +2721,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2713,14 +2741,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2730,18 +2758,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>001/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2749,11 +2777,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2771,14 +2795,14 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-ca205f0874380f69</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2786,14 +2810,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2803,18 +2827,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta jurisdicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2840,14 +2864,14 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-24e9015ecceeff7f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2855,29 +2879,25 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>INSTITUTO CARBÓ S.R.L</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>01/2026</t>
-        </is>
-      </c>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2909,14 +2929,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-6aa57c7437a30ca3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2931,7 +2951,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2941,18 +2961,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2960,11 +2980,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K34" s="4" t="inlineStr"/>
       <c r="L34" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2977,12 +2993,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
@@ -2997,14 +3013,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3014,18 +3030,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3033,7 +3049,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -3046,12 +3066,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -3073,24 +3093,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3111,12 +3135,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -3138,28 +3162,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3167,7 +3191,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -3180,19 +3208,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3200,14 +3228,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3217,18 +3245,18 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3249,19 +3277,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-9ca2387eef6d6fc1</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3269,35 +3297,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>240/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3318,12 +3342,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -3338,29 +3362,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -3387,17 +3411,224 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>id-9a16884dd5a64a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>08/26</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>id-9ca2387eef6d6fc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>240/26</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Ver el sitio</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Poder Judicial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>id-ba80195eeddbd2bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>ENERSA</t>
         </is>
       </c>
-      <c r="O40" s="4" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O43"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3477,6 +3708,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,11 +57,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
@@ -73,6 +68,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -572,7 +572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -582,27 +582,27 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Vehículos</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE VILLA ELISA (E.R.)</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>004/26</t>
+          <t>86/2026</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE UN (1) VEHÍCULO PARA TRANSPORTE DE PASAJEROS DE (5) CINCO PLAZAS 0 KM - MODELO/AÑO 2026, PARA LA MUNICIPALIDAD DE LA CIUDAD DE VILLA ELISA, ENTRE RÍOS</t>
+          <t>ADQUISICION DE CAL VIVA AEREA</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>01 de OCTUBRE de 2026 a la hora 10:00 en la Oficina de Compras de la Municipalidad de Villa Elisa, Entre Ríos</t>
+          <t>01-10-2026 08:00</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -620,11 +620,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$ 20.000,00 (Pesos Veinte mil con 00/100) el que se puede adquirir en </t>
-        </is>
-      </c>
+      <c r="K2" s="4" t="inlineStr"/>
       <c r="L2" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -637,19 +633,19 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>id-0132097e777a3442</t>
+          <t>id-ee4153887a6e1e8d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -659,37 +655,37 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>86/2026</t>
+          <t>016/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAL VIVA AEREA</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>01-10-2026 08:00</t>
+          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -697,7 +693,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -710,19 +710,19 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-ee4153887a6e1e8d</t>
+          <t>id-53f1430f94acb0b0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -747,22 +747,22 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>016/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>06/10/2026 HORA: 11:00 HS</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -792,14 +792,14 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-53f1430f94acb0b0</t>
+          <t>id-65d18d99bf0b2c6c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -807,29 +807,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>PARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -839,19 +839,15 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026 HORA: 11:00 HS</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -869,7 +865,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-65d18d99bf0b2c6c</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
@@ -884,44 +880,44 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE SALUD</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Licitación Publica</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -942,14 +938,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-3312d89e1a3e2e53</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -957,9 +953,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -974,22 +970,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>31/2026</t>
+          <t>32/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>07 de octubre de 2026 Hora: 10:00</t>
+          <t>08 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1015,7 +1011,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-76d9566cb30a6df5</t>
+          <t>id-0ace7de8f16d3baf</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1028,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1047,12 +1043,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>32/2026</t>
+          <t>33/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1062,7 +1058,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 10:00</t>
+          <t>08 de octubre de 2026 Hora: 11:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1088,7 +1084,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-0ace7de8f16d3baf</t>
+          <t>id-fe71ac2aaf71b8d8</t>
         </is>
       </c>
     </row>
@@ -1103,14 +1099,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1120,22 +1116,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>33/2026</t>
+          <t>34/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 11:00</t>
+          <t>09 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1161,14 +1157,14 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-fe71ac2aaf71b8d8</t>
+          <t>id-b147fbd9d3081bfc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1176,14 +1172,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Vehículos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1193,12 +1189,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>34/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1208,7 +1204,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>09 de octubre de 2026 Hora: 10:00</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1216,7 +1212,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+        </is>
+      </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-b147fbd9d3081bfc</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
@@ -1249,14 +1249,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>13/10/2026 HORA: 10: 00 HS</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1311,14 +1311,14 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1358,19 +1358,15 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10: 00 HS</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1388,7 +1384,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-1a2561509308b1b6</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1399,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1420,12 +1416,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1435,7 +1431,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1461,7 +1457,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1472,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1493,12 +1489,12 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1508,7 +1504,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1534,14 +1530,14 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1551,12 +1547,12 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1566,27 +1562,27 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>008/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -1607,14 +1603,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-a9af9f59c8c487c8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1622,14 +1618,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1637,24 +1633,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>008/2026</t>
-        </is>
-      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
+          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1662,7 +1654,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1680,7 +1676,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-a9af9f59c8c487c8</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
@@ -1695,14 +1691,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1713,17 +1709,17 @@
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1753,14 +1749,14 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1770,12 +1766,12 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1783,20 +1779,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>11/26</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-86cc9c230734c462</t>
         </is>
       </c>
     </row>
@@ -1841,14 +1841,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
+          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
+          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1881,11 +1881,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1898,19 +1894,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-86cc9c230734c462</t>
+          <t>id-322a40f5e43af35d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1918,47 +1914,51 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr"/>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>$25.000,00</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-322a40f5e43af35d</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -1991,14 +1991,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2008,30 +2008,34 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2049,7 +2053,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2064,49 +2068,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2121,12 +2125,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2141,14 +2145,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2158,22 +2162,22 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2181,11 +2185,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2198,34 +2198,34 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2235,22 +2235,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>001/26</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2258,11 +2254,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2280,29 +2272,29 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-ca205f0874380f69</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2312,22 +2304,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2348,12 +2336,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-24e9015ecceeff7f</t>
         </is>
       </c>
     </row>
@@ -2368,35 +2356,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
+          <t>INSTITUTO CARBÓ S.R.L</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>001/26</t>
-        </is>
-      </c>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2422,14 +2406,14 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-ca205f0874380f69</t>
+          <t>id-6aa57c7437a30ca3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2437,14 +2421,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2454,18 +2438,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2491,14 +2475,14 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-24e9015ecceeff7f</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2508,29 +2492,33 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>INSTITUTO CARBÓ S.R.L</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>001-2026</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2538,7 +2526,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2556,14 +2548,14 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-6aa57c7437a30ca3</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2571,14 +2563,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2588,12 +2580,12 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2625,14 +2617,14 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2640,14 +2632,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2657,18 +2649,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2676,11 +2668,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2693,19 +2681,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-9ca2387eef6d6fc1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2713,35 +2701,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>240/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2762,12 +2750,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2770,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
@@ -2847,7 +2835,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2916,7 +2904,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
@@ -2977,7 +2965,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2985,14 +2973,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3002,18 +2990,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3034,19 +3022,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-9ca2387eef6d6fc1</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3054,35 +3042,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>240/26</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3103,12 +3091,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3111,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -3140,18 +3128,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3177,7 +3165,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3180,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -3209,18 +3197,18 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3246,7 +3234,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3249,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -3278,18 +3266,18 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3315,7 +3303,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3318,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -3345,20 +3333,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>05/2025</t>
-        </is>
-      </c>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3384,7 +3368,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3383,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -3416,18 +3400,18 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3453,7 +3437,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3452,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -3483,16 +3467,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3518,14 +3506,14 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3533,7 +3521,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -3550,18 +3538,18 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -3587,14 +3575,14 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3602,7 +3590,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -3619,18 +3607,18 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3656,150 +3644,12 @@
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O45" s="4" t="inlineStr">
-        <is>
-          <t>id-07ddb93a12c5a870</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>Concurso de Precio N° 02/2025</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O46" s="4" t="inlineStr">
-        <is>
           <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3887,10 +3737,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,11 +57,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
@@ -73,6 +68,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E6D9F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -582,12 +582,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Vehículos</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE VILLA ELISA (E.R.)</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -597,22 +597,22 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>004/26</t>
+          <t>016/2026</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE UN (1) VEHÍCULO PARA TRANSPORTE DE PASAJEROS DE (5) CINCO PLAZAS 0 KM - MODELO/AÑO 2026, PARA LA MUNICIPALIDAD DE LA CIUDAD DE VILLA ELISA, ENTRE RÍOS</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>01 de OCTUBRE de 2026 a la hora 10:00 en la Oficina de Compras de la Municipalidad de Villa Elisa, Entre Ríos</t>
+          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">$ 20.000,00 (Pesos Veinte mil con 00/100) el que se puede adquirir en </t>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
@@ -642,14 +642,14 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>id-0132097e777a3442</t>
+          <t>id-53f1430f94acb0b0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>016/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>06/10/2026 HORA: 11:00 HS</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -719,14 +719,14 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-53f1430f94acb0b0</t>
+          <t>id-65d18d99bf0b2c6c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -734,29 +734,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>PARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -766,19 +766,15 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026 HORA: 11:00 HS</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -796,7 +792,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-65d18d99bf0b2c6c</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
@@ -811,44 +807,44 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE SALUD</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Licitación Publica</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
@@ -869,14 +865,14 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-3312d89e1a3e2e53</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -884,9 +880,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -901,22 +897,22 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>31/2026</t>
+          <t>32/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>07 de octubre de 2026 Hora: 10:00</t>
+          <t>08 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +938,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-76d9566cb30a6df5</t>
+          <t>id-0ace7de8f16d3baf</t>
         </is>
       </c>
     </row>
@@ -957,9 +953,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -974,12 +970,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>32/2026</t>
+          <t>33/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 10:00</t>
+          <t>08 de octubre de 2026 Hora: 11:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1015,7 +1011,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-0ace7de8f16d3baf</t>
+          <t>id-fe71ac2aaf71b8d8</t>
         </is>
       </c>
     </row>
@@ -1030,14 +1026,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1047,22 +1043,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>33/2026</t>
+          <t>34/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 11:00</t>
+          <t>09 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1088,14 +1084,14 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-fe71ac2aaf71b8d8</t>
+          <t>id-b147fbd9d3081bfc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1103,14 +1099,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Vehículos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1120,12 +1116,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>34/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1135,7 +1131,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>09 de octubre de 2026 Hora: 10:00</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1143,7 +1139,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-b147fbd9d3081bfc</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Vehículos</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>13/10/2026 HORA: 10: 00 HS</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1285,19 +1285,15 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10: 00 HS</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1315,7 +1311,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-1a2561509308b1b6</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1326,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1347,12 +1343,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1362,7 +1358,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1388,7 +1384,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1399,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1420,12 +1416,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1435,7 +1431,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1461,14 +1457,14 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1476,14 +1472,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1491,32 +1487,32 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>12/2026</t>
-        </is>
-      </c>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“ADQUISICIÓN DE MATERIALES ELÉCTRICOS PARA EJECUCIÓN DEL PROYECTO DE RECONVERSIÓN Y OPTIMIZACIÓN DEL ALUMBRADO PÚBLICO DE LA CIUDAD DE COLÓN”</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>14 de OCTUBRE de 2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1534,7 +1530,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-9e122d52de12ffef</t>
         </is>
       </c>
     </row>
@@ -1549,14 +1545,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE COLON</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1564,10 +1560,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>017/2026</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES ELÉCTRICOS PARA EJECUCIÓN DEL PROYECTO DE RECONVERSIÓN Y OPTIMIZACIÓN DEL ALUMBRADO PÚBLICO DE LA CIUDAD DE COLÓN”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de UNA (1) MOTONIVELADORA, nueva, sin uso, cero km, con una potencia entre 220/240 HP, con opción a implementos, que será utilizada para el área del corralón municipal</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>14 de OCTUBRE de 2026</t>
+          <t>14 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>$100.000,00. - (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -1607,14 +1607,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-9e122d52de12ffef</t>
+          <t>id-4c3b33859e596759</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1622,14 +1622,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Vehículos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>017/2026</t>
+          <t>008/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de UNA (1) MOTONIVELADORA, nueva, sin uso, cero km, con una potencia entre 220/240 HP, con opción a implementos, que será utilizada para el área del corralón municipal</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>14 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1662,11 +1662,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>$100.000,00. - (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
-        </is>
-      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1684,14 +1680,14 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-4c3b33859e596759</t>
+          <t>id-a9af9f59c8c487c8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1699,14 +1695,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
+          <t>MINISTERIO DE SALUD — GOBIERNO DE ENTRE RIOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1716,22 +1712,22 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>008/2026</t>
+          <t>18/26</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
+          <t>Adquirir Sesenta Mil (60.000) Kilogramos de Leche Entera en Polvo Instantánea, Fortificada con Hierro, Zinc y Ácido Ascórbico</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1739,7 +1735,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>PESOS TRES MIL QUINIENTOS ($ 3.500,00)</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-a9af9f59c8c487c8</t>
+          <t>id-04a917d50ccab2e3</t>
         </is>
       </c>
     </row>
@@ -1772,14 +1772,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MINISTERIO DE SALUD — GOBIERNO DE ENTRE RIOS</t>
+          <t>VILLAGUAY — MUNICIPALIDAD DE VILLAGUAY</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1787,14 +1787,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>18/26</t>
-        </is>
-      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Sesenta Mil (60.000) Kilogramos de Leche Entera en Polvo Instantánea, Fortificada con Hierro, Zinc y Ácido Ascórbico</t>
+          <t>Contratación, ejecución, liquidación, pago y recepción de la obra destinada a la elaboración del Proyecto Ejecutivo, provisión de materiales, mano de obra, equipos, ejecución, ensayos, habilitación y puesta en servicio de la instalación de gas natural para la Planta Municipal de Elaboración de Mezcla Asfáltica en Caliente, ubicada en el Lote N.º 4 de la Chacra N.º 263 del Parque Industrial de Villaguay, Provincia de Entre Ríos. La contratación comprenderá una solución integral bajo modalidad “llave en mano”, incluyendo todos los trabajos, provisiones, trámites, representaciones técnicas, inspe</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1804,7 +1800,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>16 de octubre del año 2026 a las 10:00 Horas, la que se realizara en la Ofic ina de suministros de la Municipalidad de V</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1814,7 +1810,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>PESOS TRES MIL QUINIENTOS ($ 3.500,00)</t>
+          <t>$ 50.000,00</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1834,14 +1830,14 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-04a917d50ccab2e3</t>
+          <t>id-55f1e5ca423a9262</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1849,14 +1845,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VILLAGUAY — MUNICIPALIDAD DE VILLAGUAY</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1867,17 +1863,17 @@
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Contratación, ejecución, liquidación, pago y recepción de la obra destinada a la elaboración del Proyecto Ejecutivo, provisión de materiales, mano de obra, equipos, ejecución, ensayos, habilitación y puesta en servicio de la instalación de gas natural para la Planta Municipal de Elaboración de Mezcla Asfáltica en Caliente, ubicada en el Lote N.º 4 de la Chacra N.º 263 del Parque Industrial de Villaguay, Provincia de Entre Ríos. La contratación comprenderá una solución integral bajo modalidad “llave en mano”, incluyendo todos los trabajos, provisiones, trámites, representaciones técnicas, inspe</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>16 de octubre del año 2026 a las 10:00 Horas, la que se realizara en la Ofic ina de suministros de la Municipalidad de V</t>
+          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1887,7 +1883,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>$ 50.000,00</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1907,14 +1903,14 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-55f1e5ca423a9262</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1922,35 +1918,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
+          <t>CONCURSO DE PRECIOS</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>304/2026</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1958,11 +1958,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1975,19 +1971,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1995,39 +1991,35 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>304/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2035,7 +2027,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2048,19 +2044,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2070,33 +2066,37 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
+          <t>LICITACIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>82/2026</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2104,11 +2104,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2121,19 +2117,19 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2141,39 +2137,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>82/2026</t>
+          <t>11/26</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2181,7 +2177,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2194,12 +2194,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-86cc9c230734c462</t>
         </is>
       </c>
     </row>
@@ -2214,14 +2214,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
+          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
+          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2254,11 +2254,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2271,19 +2267,19 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-86cc9c230734c462</t>
+          <t>id-322a40f5e43af35d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2291,14 +2287,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2308,22 +2304,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2331,7 +2327,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-322a40f5e43af35d</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2364,14 +2364,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CRESPO -- ENTRE RÍOS</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2381,30 +2381,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de modulo canal premoldeado cajón tipo pórtico de 2,00 X 1,00 (interior) X 1,00 mts. de longitud de hormigón para canalizar calle Los Quechuas al final</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>28 de septiembre de 2026 10:00 Hs. Lugar: Sección Suministros, Palacio Municipal sito en 25 de mayo Nº 943, C</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2422,7 +2426,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-61e8747a99305fe9</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2437,51 +2441,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas Ver acta</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>$25.000,00</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2494,34 +2494,34 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Vehículos</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2531,22 +2531,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>001/26</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
+          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2554,11 +2550,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2576,29 +2568,29 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-ca205f0874380f69</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2608,22 +2600,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta jurisdicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2631,11 +2619,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2653,54 +2637,46 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-24e9015ecceeff7f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>INSTITUTO CARBÓ S.R.L</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2721,19 +2697,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-6aa57c7437a30ca3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2743,12 +2719,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Vehículos</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2758,18 +2734,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>001/26</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2795,14 +2771,14 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-ca205f0874380f69</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2810,14 +2786,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2827,18 +2803,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta jurisdicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2846,7 +2822,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2864,14 +2844,14 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-24e9015ecceeff7f</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2879,25 +2859,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>INSTITUTO CARBÓ S.R.L</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2929,14 +2913,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-6aa57c7437a30ca3</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2944,14 +2928,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2961,18 +2945,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2980,7 +2964,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2993,12 +2981,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3013,14 +3001,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3030,18 +3018,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3049,11 +3037,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -3066,12 +3050,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3086,35 +3070,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>04/2026</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3135,12 +3115,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -3155,35 +3135,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3191,11 +3171,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K37" s="4" t="inlineStr"/>
       <c r="L37" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -3208,19 +3184,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3230,12 +3206,12 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3245,18 +3221,18 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3277,19 +3253,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-9ca2387eef6d6fc1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3297,31 +3273,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr"/>
+          <t>Solicitud de Cotización</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>240/26</t>
+        </is>
+      </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3342,12 +3322,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
@@ -3362,29 +3342,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -3411,224 +3391,17 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>25/09/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>08/26</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>id-9ca2387eef6d6fc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>240/26</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Ver el sitio</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Poder Judicial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>id-ba80195eeddbd2bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O43"/>
+  <autoFilter ref="A1:O40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3708,12 +3481,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1991,14 +1991,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2008,22 +2008,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2108,11 +2108,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2125,34 +2121,34 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2162,22 +2158,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>001/26</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2198,12 +2190,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-ca205f0874380f69</t>
         </is>
       </c>
     </row>
@@ -2218,14 +2210,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2235,18 +2227,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>001/26</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
+          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2272,7 +2264,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-ca205f0874380f69</t>
+          <t>id-24e9015ecceeff7f</t>
         </is>
       </c>
     </row>
@@ -2287,35 +2279,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>INSTITUTO CARBÓ S.R.L</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2341,14 +2329,14 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-24e9015ecceeff7f</t>
+          <t>id-6aa57c7437a30ca3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2363,18 +2351,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>INSTITUTO CARBÓ S.R.L</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>08/26</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
+          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -2406,14 +2398,14 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-6aa57c7437a30ca3</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2421,14 +2413,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2438,18 +2430,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2457,7 +2449,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2475,7 +2471,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2490,14 +2486,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2507,18 +2503,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2526,11 +2522,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2548,14 +2540,14 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2563,14 +2555,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2580,18 +2572,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2612,19 +2604,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-9ca2387eef6d6fc1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2644,17 +2636,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>240/26</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -2686,14 +2678,14 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-9ca2387eef6d6fc1</t>
+          <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2701,35 +2693,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>240/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2750,12 +2738,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2770,9 +2758,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2782,13 +2770,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -2820,7 +2812,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2835,29 +2827,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2884,19 +2876,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2904,35 +2896,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2953,12 +2945,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2990,18 +2982,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3027,7 +3019,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -3059,18 +3051,18 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3096,7 +3088,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -3128,18 +3120,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3165,7 +3157,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -3197,18 +3189,18 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3234,7 +3226,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -3264,20 +3256,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>06/2025</t>
-        </is>
-      </c>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3303,7 +3291,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -3333,16 +3321,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3368,7 +3360,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -3400,18 +3392,18 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3437,14 +3429,14 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3469,18 +3461,18 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3506,7 +3498,7 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3543,13 +3535,13 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -3575,81 +3567,12 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>Concurso de Precio N° 02/2025</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O44" s="4" t="inlineStr">
-        <is>
           <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O44"/>
+  <autoFilter ref="A1:O43"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3735,8 +3658,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1537,7 +1537,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1545,14 +1545,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>DIAMANTE — COMUNA ALDEA PROTESTANTE -- DIAMANTE -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>017/2026</t>
+          <t>03/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de UNA (1) MOTONIVELADORA, nueva, sin uso, cero km, con una potencia entre 220/240 HP, con opción a implementos, que será utilizada para el área del corralón municipal</t>
+          <t>Conforme a lo autorizado por decreto Nº 290/26 llámese a licitación pública Nº 03/26 con el objeto de comprar 10 toneladas de emulsión catiónica súper estable (asfalto de imprimación), puesto en Aldea Protestante</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>14 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>miércoles 14 de octubre de 2026 – Hora nueve (09:00) Lugar de presentación de la oferta: Sede Comuna Aldea Protestan</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1585,11 +1585,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>$100.000,00. - (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
-        </is>
-      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1607,14 +1603,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-4c3b33859e596759</t>
+          <t>id-c2f3a25cfb37fd38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1629,7 +1625,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1639,12 +1635,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>008/2026</t>
+          <t>017/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de UNA (1) MOTONIVELADORA, nueva, sin uso, cero km, con una potencia entre 220/240 HP, con opción a implementos, que será utilizada para el área del corralón municipal</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1654,7 +1650,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
+          <t>14 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1662,7 +1658,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>$100.000,00. - (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1680,14 +1680,14 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-a9af9f59c8c487c8</t>
+          <t>id-4c3b33859e596759</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1695,14 +1695,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MINISTERIO DE SALUD — GOBIERNO DE ENTRE RIOS</t>
+          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1712,22 +1712,22 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>008/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Sesenta Mil (60.000) Kilogramos de Leche Entera en Polvo Instantánea, Fortificada con Hierro, Zinc y Ácido Ascórbico</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1735,11 +1735,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>PESOS TRES MIL QUINIENTOS ($ 3.500,00)</t>
-        </is>
-      </c>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1757,7 +1753,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-04a917d50ccab2e3</t>
+          <t>id-a9af9f59c8c487c8</t>
         </is>
       </c>
     </row>
@@ -1772,14 +1768,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VILLAGUAY — MUNICIPALIDAD DE VILLAGUAY</t>
+          <t>MINISTERIO DE SALUD — GOBIERNO DE ENTRE RIOS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1787,10 +1783,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>18/26</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Contratación, ejecución, liquidación, pago y recepción de la obra destinada a la elaboración del Proyecto Ejecutivo, provisión de materiales, mano de obra, equipos, ejecución, ensayos, habilitación y puesta en servicio de la instalación de gas natural para la Planta Municipal de Elaboración de Mezcla Asfáltica en Caliente, ubicada en el Lote N.º 4 de la Chacra N.º 263 del Parque Industrial de Villaguay, Provincia de Entre Ríos. La contratación comprenderá una solución integral bajo modalidad “llave en mano”, incluyendo todos los trabajos, provisiones, trámites, representaciones técnicas, inspe</t>
+          <t>Adquirir Sesenta Mil (60.000) Kilogramos de Leche Entera en Polvo Instantánea, Fortificada con Hierro, Zinc y Ácido Ascórbico</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>16 de octubre del año 2026 a las 10:00 Horas, la que se realizara en la Ofic ina de suministros de la Municipalidad de V</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>$ 50.000,00</t>
+          <t>PESOS TRES MIL QUINIENTOS ($ 3.500,00)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1830,14 +1830,14 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-55f1e5ca423a9262</t>
+          <t>id-04a917d50ccab2e3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>VILLAGUAY — MUNICIPALIDAD DE VILLAGUAY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1863,17 +1863,17 @@
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>Contratación, ejecución, liquidación, pago y recepción de la obra destinada a la elaboración del Proyecto Ejecutivo, provisión de materiales, mano de obra, equipos, ejecución, ensayos, habilitación y puesta en servicio de la instalación de gas natural para la Planta Municipal de Elaboración de Mezcla Asfáltica en Caliente, ubicada en el Lote N.º 4 de la Chacra N.º 263 del Parque Industrial de Villaguay, Provincia de Entre Ríos. La contratación comprenderá una solución i ntegral bajo modalidad “llave en mano”, incluyendo todos los trabajos, provisiones, trámites, representaciones técnicas, insp</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>16 de octubre del año 2026 a las 10:00 Horas, la que se realizara en la Ofici na de suministros de la Municipalidad de V</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>$ 50.000,00</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-55f1e5ca423a9262</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1925,32 +1925,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>304/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>21-09-2026 08:15</t>
+          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1958,7 +1954,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1971,19 +1971,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-cb965eafa60519ea</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1998,28 +1998,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
+          <t>CONCURSO DE PRECIOS</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>304/2026</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>PROVISION E INSTALACION DE SISTEMA DE ILUMINACION</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>21-09-2026 08:15</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2027,11 +2031,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2044,19 +2044,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-cb965eafa60519ea</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2064,39 +2064,35 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>82/2026</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>22-09-2026 08:00</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2104,7 +2100,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2117,19 +2117,19 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-e31ab37f1904ce3b</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2144,32 +2144,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>82/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
+          <t>CONTRATACION DE SERVICIO DE MANO DE OBRA PARA ACONDICIONAMIENTO DE TECHO</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
+          <t>22-09-2026 08:00</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2177,11 +2177,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2194,12 +2190,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-86cc9c230734c462</t>
+          <t>id-e31ab37f1904ce3b</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2217,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2231,12 +2227,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>11/26</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2246,7 +2242,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2254,7 +2250,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2267,19 +2267,19 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-322a40f5e43af35d</t>
+          <t>id-86cc9c230734c462</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2287,14 +2287,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2304,22 +2304,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
+          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2327,11 +2327,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2344,12 +2340,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-322a40f5e43af35d</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3261,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3273,35 +3269,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>240/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3322,86 +3318,17 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
           <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O39"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3479,8 +3406,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2031,11 +2031,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2048,34 +2044,34 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2085,22 +2081,18 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>001/26</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2121,12 +2113,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-ca205f0874380f69</t>
         </is>
       </c>
     </row>
@@ -2141,14 +2133,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2158,18 +2150,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>001/26</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
+          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
+          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2195,7 +2187,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-ca205f0874380f69</t>
+          <t>id-24e9015ecceeff7f</t>
         </is>
       </c>
     </row>
@@ -2210,35 +2202,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>INSTITUTO CARBÓ S.R.L</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2264,14 +2252,14 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-24e9015ecceeff7f</t>
+          <t>id-6aa57c7437a30ca3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2286,18 +2274,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>INSTITUTO CARBÓ S.R.L</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>08/26</t>
+        </is>
+      </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
+          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -2329,14 +2321,14 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-6aa57c7437a30ca3</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2344,14 +2336,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2361,18 +2353,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2380,7 +2372,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2398,7 +2394,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2413,14 +2409,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2430,18 +2426,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2449,11 +2445,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2471,14 +2463,14 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2486,14 +2478,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2503,18 +2495,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2535,19 +2527,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-9ca2387eef6d6fc1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2567,17 +2559,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Solicitud de Cotización</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>240/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
+          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2609,14 +2601,14 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-9ca2387eef6d6fc1</t>
+          <t>id-ba80195eeddbd2bd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2624,35 +2616,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>240/26</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2673,12 +2661,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
@@ -2693,9 +2681,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2705,13 +2693,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -2743,7 +2735,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2758,29 +2750,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -2807,19 +2799,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2827,35 +2819,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2876,12 +2868,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2913,18 +2905,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2950,7 +2942,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2982,18 +2974,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3019,7 +3011,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -3051,18 +3043,18 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3088,7 +3080,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -3120,18 +3112,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3157,7 +3149,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -3187,20 +3179,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>06/2025</t>
-        </is>
-      </c>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3226,7 +3214,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -3256,16 +3244,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3291,7 +3283,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -3323,18 +3315,18 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3360,14 +3352,14 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3392,18 +3384,18 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3429,7 +3421,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3466,13 +3458,13 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3498,81 +3490,12 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Concurso de Precio N° 02/2025</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
           <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O43"/>
+  <autoFilter ref="A1:O42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3656,8 +3579,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,7 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -67,12 +72,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -572,7 +572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -592,17 +592,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>86/2026</t>
+          <t>311/2026</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAL VIVA AEREA</t>
+          <t>ADQUISICION DE LAMPARAS PARA VEHICULOS</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>01-10-2026 08:00</t>
+          <t>01-10-2026 10:30</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -638,14 +638,14 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>id-ee4153887a6e1e8d</t>
+          <t>id-5824d400c85d33c6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -655,37 +655,37 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>CONCURSO DE PRECIOS</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>016/2026</t>
+          <t>321/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
+          <t>ALQUILER DE CARPAS, BAÑOS QUIMICOS Y DISPENSER</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>01-10-2026 11:30</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -693,11 +693,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
-        </is>
-      </c>
+      <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -710,19 +706,19 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-53f1430f94acb0b0</t>
+          <t>id-ee8fe54e83fd3889</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -732,12 +728,12 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -747,22 +743,22 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>016/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026 HORA: 11:00 HS</t>
+          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -772,7 +768,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -792,14 +788,14 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-65d18d99bf0b2c6c</t>
+          <t>id-53f1430f94acb0b0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -809,27 +805,27 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE SALUD</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Licitación Publica</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -839,15 +835,19 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>06/10/2026 HORA: 11:00 HS</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -865,7 +865,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-3312d89e1a3e2e53</t>
+          <t>id-65d18d99bf0b2c6c</t>
         </is>
       </c>
     </row>
@@ -880,44 +880,44 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>PARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>31/2026</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>07 de octubre de 2026 Hora: 10:00</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -938,14 +938,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-76d9566cb30a6df5</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -953,9 +953,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -970,22 +970,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>32/2026</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 10:00</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-0ace7de8f16d3baf</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
@@ -1026,9 +1026,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>33/2026</t>
+          <t>32/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 11:00</t>
+          <t>08 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-fe71ac2aaf71b8d8</t>
+          <t>id-0ace7de8f16d3baf</t>
         </is>
       </c>
     </row>
@@ -1099,14 +1099,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1116,22 +1116,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>34/2026</t>
+          <t>33/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>09 de octubre de 2026 Hora: 10:00</t>
+          <t>08 de octubre de 2026 Hora: 11:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1157,14 +1157,14 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-b147fbd9d3081bfc</t>
+          <t>id-fe71ac2aaf71b8d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1172,14 +1172,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Vehículos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>34/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
+          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>09 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1212,11 +1212,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
-        </is>
-      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1234,7 +1230,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-b147fbd9d3081bfc</t>
         </is>
       </c>
     </row>
@@ -1249,14 +1245,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1266,22 +1262,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10: 00 HS</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1291,7 +1287,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1311,14 +1307,14 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-1a2561509308b1b6</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1328,12 +1324,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1348,7 +1344,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1358,15 +1354,19 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>13/10/2026 HORA: 10: 00 HS</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+        </is>
+      </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>12/2026</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1530,14 +1530,14 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1545,14 +1545,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1562,27 +1562,27 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>008/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -1603,14 +1603,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-a9af9f59c8c487c8</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1618,14 +1618,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SALUD ENTRE RÍOS S.A.U</t>
+          <t>MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1636,17 +1636,17 @@
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+          <t>“ADQUISICIÓN DE MATERIALES ELÉCTRICOS PARA EJECUCIÓN DEL PROYECTO DE RECONVERSIÓN Y OPTIMIZACIÓN DEL ALUMBRADO PÚBLICO DE LA CIUDAD DE COLÓN”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
+          <t>14 de OCTUBRE de 2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1676,14 +1676,14 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-d35d5e849089d7ac</t>
+          <t>id-9e122d52de12ffef</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1691,14 +1691,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
+          <t>DIAMANTE — COMUNA ALDEA PROTESTANTE -- DIAMANTE -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1706,20 +1706,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+          <t>Conforme a lo autorizado por decreto Nº 290/26 llámese a licitación pública Nº 03/26 con el objeto de comprar 10 toneladas de emulsión catiónica súper estable (asfalto de imprimación), puesto en Aldea Protestante</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
+          <t>miércoles 14 de octubre de 2026 – Hora nueve (09:00) Lugar de presentación de la oferta: Sede Comuna Aldea Protestan</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1727,11 +1731,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1749,14 +1749,14 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-6b955df9d3f6241a</t>
+          <t>id-c2f3a25cfb37fd38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1764,14 +1764,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>017/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de UNA (1) MOTONIVELADORA, nueva, sin uso, cero km, con una potencia entre 220/240 HP, con opción a implementos, que será utilizada para el área del corralón municipal</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
+          <t>14 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>$100.000,00. - (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-86cc9c230734c462</t>
+          <t>id-4c3b33859e596759</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1841,14 +1841,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>VICTORIA — MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>008/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
+          <t>Proveer a la Municipalidad de Victoria, Entre Ríos, de Veinticinco Mil (25.000) litros de Diésel 500, para movilidad de vehículos y maquinarias viales , Ocho Mil (8.000) litros de Gasoil Tipo euro o similar y Ocho (8.000) litros de nafta súper para vehículos y áreas afectadas a la Secretaria de Planeamiento y Dirección de Ambiente y Desarrollo sostenible;</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
+          <t>14 de octubre de 2026 a las 09:00 hs., en la Oficina de Compras de la Municipalidad de Victoria, Entr</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1894,19 +1894,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-322a40f5e43af35d</t>
+          <t>id-a9af9f59c8c487c8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1914,49 +1914,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Materiales</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>MINISTERIO DE SALUD — GOBIERNO DE ENTRE RIOS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>18/26</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
+          <t>Adquirir Sesenta Mil (60.000) Kilogramos de Leche Entera en Polvo Instantánea, Fortificada con Hierro, Zinc y Ácido Ascórbico</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>PESOS TRES MIL QUINIENTOS ($ 3.500,00)</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1971,19 +1971,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-04a917d50ccab2e3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>VILLAGUAY — MUNICIPALIDAD DE VILLAGUAY</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2006,24 +2006,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Contratación, ejecución, liquidación, pago y recepción de la obra destinada a la elaboración del Proyecto Ejecutivo, provisión de materiales, mano de obra, equipos, ejecución, ensayos, habilitación y puesta en servicio de la instalación de gas natural para la Planta Municipal de Elaboración de Mezcla Asfáltica en Caliente, ubicada en el Lote N.º 4 de la Chacra N.º 263 del Parque Industrial de Villaguay, Provincia de Entre Ríos. La contratación comprenderá una solución i ntegral bajo modalidad “llave en mano”, incluyendo todos los trabajos, provisiones, trámites, representaciones técnicas, insp</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>16 de octubre del año 2026 a las 10:00 Horas, la que se realizara en la Ofici na de suministros de la Municipalidad de V</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2031,7 +2027,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>$ 50.000,00</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2044,34 +2044,34 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-55f1e5ca423a9262</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
+          <t>SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2079,20 +2079,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>001/26</t>
-        </is>
-      </c>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>Contratación de Servicio de Viandas para el Hospital de la Baxada</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
+          <t>Hospital de la Baxada, calle Gral. Al varado Nº 2.250 Paraná, Entre Ríos, el día 19/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2100,7 +2100,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2118,29 +2122,29 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-ca205f0874380f69</t>
+          <t>id-d35d5e849089d7ac</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>PARANA — SALUD ENTRE RÍOS S.A.U</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2148,20 +2152,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta juris dicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
+          <t>Servicio de Recolección, Lavado, Desinfección, Secado, Planchado y Transporte de Ropa Hospitalaria</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
+          <t>Hospital de la Baxada, calle Gral. Alvarado Nº 2.250 Paraná, Entre Ríos, el día 21/10/2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2169,7 +2173,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2187,7 +2195,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-24e9015ecceeff7f</t>
+          <t>id-6b955df9d3f6241a</t>
         </is>
       </c>
     </row>
@@ -2197,36 +2205,44 @@
           <t>26/09/2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>INSTITUTO CARBÓ S.R.L</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>11/26</t>
+        </is>
+      </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “TERMINACION ESCUELA Nº 40 “JOSÉ ENRIQUE RODÓ”-SEPTIMO DISTRITO-DEPARTAMENTO GUALEGUAY.”</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>DE LAS OFERTAS: el día 23 de Octubre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2234,7 +2250,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2252,29 +2272,29 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-6aa57c7437a30ca3</t>
+          <t>id-86cc9c230734c462</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VIALE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2284,18 +2304,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>Terminación Escuela N° 40 "José Enrique Rodó", Séptimo Distrito</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>viernes, 23 de octubre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2316,19 +2340,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-ef1ddb923c7e7fdb</t>
+          <t>id-322a40f5e43af35d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,14 +2360,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>ISLAS DEL IBICUY — MUNICIPALIDAD DE VILLA PARANACITO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2353,18 +2377,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>001/26</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>ADQUISICIÓN de UN (1) FURGON UTILITARIO CHICO con 5 asientos 0 KM. con destino a Subsecretaria de Asistencia Directa y Emergencia</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>DE LAS PROPUESTAS: 20 de Octubre de 2.026, a las 11:00 Hs. en el salón de reuniones sito en Av. Entre Rios 941 de la loc</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2372,11 +2396,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2394,14 +2414,14 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-ca205f0874380f69</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2409,14 +2429,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2426,18 +2446,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>Transporte de mil doscientos cincuenta metros cúbicos (1.250 m³) de broza grillada desde Cantera “Tayreta” (Ruta Nacional N° 14 km 135) hasta jurisdicción de la comuna, de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Viernes 09 de octubre del corriente año a las 10:00 hs en la Oficina de la Sede de la Comuna</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2463,7 +2483,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-24e9015ecceeff7f</t>
         </is>
       </c>
     </row>
@@ -2480,33 +2500,29 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>INSTITUTO CARBÓ S.R.L</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>08/26</t>
-        </is>
-      </c>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
+          <t>sin internación en materia de salud, pre- hospitalarias, atención médica, domiciliaria y traslados sanitarios de alta</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2527,19 +2543,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-9ca2387eef6d6fc1</t>
+          <t>id-6aa57c7437a30ca3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2549,33 +2565,33 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>MUNICIPALIDAD DE VIALE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Solicitud de Cotización</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>240/26</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Contratación del servicio de reparación prioritaria de seis (6) escalones de mármol de la escalera de acceso al entrepiso y primer piso del Edificio Tribunales de Gualeguaychú sito en calle Roque Sáenz Peña N°94.</t>
+          <t>de asf alto 70-16 destinado a la producción de pavimento de la Planta Asfáltica, y que a continuación se detalla y</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver el sitio</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2596,12 +2612,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Poder Judicial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-ba80195eeddbd2bd</t>
+          <t>id-ef1ddb923c7e7fdb</t>
         </is>
       </c>
     </row>
@@ -2616,31 +2632,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>001-2026</t>
+        </is>
+      </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2648,7 +2668,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2661,12 +2685,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-654eebef400f89cd</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2681,35 +2705,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2730,12 +2754,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2750,35 +2774,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2786,7 +2810,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2799,19 +2827,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2819,7 +2847,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2836,18 +2864,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2873,14 +2901,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2888,35 +2916,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>02/2026</t>
-        </is>
-      </c>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>REFUERZO DE SEÑALIZACIÓN VERTICAL EN ZONA TÚNEL SUBFLUVIAL – TRAMO: ACC. TÚNEL SUBFLUVIAL “RAÚL URANGA – CARLOS SILVESTRE BEGNIS” – AV. CIRCUNVALACIÓN JOSÉ HERNÁNDEZ – DISTRITO SAUCE – DEPARTAMENTO PARANÁ – ZONAL XIX PARANÁ. – CONSULTA DE PLIEGOS: www.dpver.gov.ar – despacho.licitaciones@vialidadentrerios.gob.ar APERTURA DE LAS OFERTAS: El Acto de Apertura de las propuestas se llevará […]</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2937,19 +2961,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-654eebef400f89cd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2957,35 +2981,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3006,19 +3030,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3026,35 +3050,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3075,19 +3099,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3097,12 +3121,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3112,18 +3136,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>Obra “Readecuación del sistema de climatización –ala sur- Edificio Tribunales Gualeguay”.</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Ver el sitio</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3144,358 +3168,17 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Poder Judicial de Entre Ríos</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>20/09/2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="inlineStr">
-        <is>
-          <t>id-ebeeb6a87e688d85</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>20/09/2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>04/2025</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>id-34c85bcdb9b1123f</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>20/09/2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>03/2025</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>id-75bfffae63b7eedc</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>id-07ddb93a12c5a870</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Concurso de Precio N° 02/2025</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-9ca2387eef6d6fc1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O37"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3569,16 +3252,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,7 +57,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00E6D9F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6D9F2"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -582,37 +582,37 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Vehículos</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>311/2026</t>
+          <t>016/2026</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE LAMPARAS PARA VEHICULOS</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>01-10-2026 10:30</t>
+          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -620,7 +620,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -633,12 +637,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>id-5824d400c85d33c6</t>
+          <t>id-53f1430f94acb0b0</t>
         </is>
       </c>
     </row>
@@ -660,32 +664,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>321/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>ALQUILER DE CARPAS, BAÑOS QUIMICOS Y DISPENSER</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>01-10-2026 11:30</t>
+          <t>06/10/2026 HORA: 11:00 HS</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -693,7 +697,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -706,19 +714,19 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-ee8fe54e83fd3889</t>
+          <t>id-65d18d99bf0b2c6c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -726,51 +734,47 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>PARANA — MINISTERIO DE SALUD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Publica</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>016/2026</t>
+          <t>17/26</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de mano de obra, materiales y equipamiento para ejecución de restitución de galibo y repavimentación en Avenida Belgrano y Avenida 1° de Mayo de esta ciudad de chajari</t>
+          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>02 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>$ 100.000, 00. - (PESOS CIEN MIL CON 00/100)</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -788,14 +792,14 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-53f1430f94acb0b0</t>
+          <t>id-3312d89e1a3e2e53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -803,14 +807,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -820,22 +824,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>31/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”, destinada a la obra denominada “Nueva Pileta en el Polideportivo El Aguará”,</t>
+          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026 HORA: 11:00 HS</t>
+          <t>07 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -843,11 +847,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -865,14 +865,14 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-65d18d99bf0b2c6c</t>
+          <t>id-76d9566cb30a6df5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -882,42 +882,42 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE SALUD</t>
+          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Licitación Publica</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>32/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Adquirir Una (01) Mesa de Anestesia. Destino: Hospital “San José” de Diamante, dependiente del Ministerio de Salud de la Provincia de Entre Ríos</t>
+          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Sala de reuniones de la Dirección de Contrataciones del Ministerio de Salud, sito en calle 25 de Mayo N° 181, segundo pi</t>
+          <t>08 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -938,14 +938,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-3312d89e1a3e2e53</t>
+          <t>id-0ace7de8f16d3baf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -970,22 +970,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>31/2026</t>
+          <t>33/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 03 (tres) Cuadras Barrio San Felipe”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>07 de octubre de 2026 Hora: 10:00</t>
+          <t>08 de octubre de 2026 Hora: 11:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-76d9566cb30a6df5</t>
+          <t>id-fe71ac2aaf71b8d8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1043,22 +1043,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>32/2026</t>
+          <t>34/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>"Adquisición de 835 m3 de Hormigón Calidad H25 para 08 cuadras de Pavimento", en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 10:00</t>
+          <t>09 de octubre de 2026 Hora: 10:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1084,14 +1084,14 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-0ace7de8f16d3baf</t>
+          <t>id-b147fbd9d3081bfc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1099,14 +1099,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1116,22 +1116,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>33/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“Pavimento Rígido – 04 (cuatro) Cuadras Barrio San Roque y 01 (una) Cuadra Barrio Vicente Obrego”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>08 de octubre de 2026 Hora: 11:00</t>
+          <t>09/10/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1139,7 +1139,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1157,14 +1161,14 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-fe71ac2aaf71b8d8</t>
+          <t>id-779e4cd290f2e64e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1174,12 +1178,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Vehículos</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCION DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1189,22 +1193,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>34/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“Concesión de la Explotación Comercial de un (01) Camión de Comidas Rápidas (para cubrir el total de cuatro puestos) en la Zona Joven – Parque La Salamanca de la Municipalidad de Concepción del Uruguay – Entre Ríos”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>09 de octubre de 2026 Hora: 10:00</t>
+          <t>13/10/2026 HORA: 10: 00 HS</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1212,7 +1216,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
+        </is>
+      </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1230,14 +1238,14 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-b147fbd9d3081bfc</t>
+          <t>id-1a2561509308b1b6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1245,14 +1253,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1262,34 +1270,30 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>11/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN DE UNA (1) MINICARGADORA 0 KM, CON CUCHARÓN FRONTAL DE USO GENERAL, UN (1) MARTILLO HIDRÁULICO Y UN (1) COMPACTADOR/RODILLO VIBRATORIO LISO”</t>
+          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>09/10/2026 HORA: 10:00 HS</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>($ 270.000,00) PESOS DOSCIENTOS SETENTA MIL</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1307,14 +1311,14 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-779e4cd290f2e64e</t>
+          <t>id-fc30d5c0b0589a79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1322,14 +1326,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1339,12 +1343,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>13/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>OBRA "PAVIMENTACION URBANA CALLE TRATADO DEL PILAR B° 3 DE FEBRERO - MUNICIPALIDAD DE SANTA ELENA" (Según Pliegos de Bases y condi ciones)</t>
+          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1354,19 +1358,15 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026 HORA: 10: 00 HS</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>$ 728.000,00 PESOS SETECIENTOS VEINTIOCHO MIL</t>
-        </is>
-      </c>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1384,14 +1384,14 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-1a2561509308b1b6</t>
+          <t>id-9d3847fb0e2b0929</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>11/2026</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>REFACCION EN ESCUELA N° 65 “ALMIRANTE BROWN” – CIUDAD DE CONCORDIA - DEPARTAMENTO CONCORDIA - PROVINCIA DE ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 09:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-fc30d5c0b0589a79</t>
+          <t>id-059239b424b9c936</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1472,14 +1472,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>13/2026</t>
+          <t>87/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>REPARACIONES VARIAS EN C. P. E. F. Nº 3 “PROFESOR HUGO LA NASA” – CIUDAD DE CONCEPCION DEL URUGUAY - DEPARTAMENTO URUGUAY - PROVINCIA D E ENTRE RÍOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Contratar la ejecución de la obra denominada “Construcción de Red Cloacal Subsidiaria del Colector Noroeste Barrio Ciudad Paisaje”</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1504,15 +1504,19 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>martes, 13 de octubre de 2026 a las 10:00</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>$ 10.000 (pesos diez mil)</t>
+        </is>
+      </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1525,19 +1529,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-9d3847fb0e2b0929</t>
+          <t>id-ceeb594e8bcc4ff7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1545,14 +1549,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL — DE SALTO GRANDE</t>
+          <t>MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1560,32 +1564,32 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>12/2026</t>
-        </is>
-      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>RECAMBIO DE CUBIERTA Y REPARACIONES VARIAS EN ESCUELA Nº 92 “CONGRESO DE TUCUMAN” – CONCEPCION DEL URUGUAY - DPTO. URUGUAY – PROVINCIA DE ENTRE RIOS de acuerdo a las c ondiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“ADQUISICIÓN DE MATERIALES ELÉCTRICOS PARA EJECUCIÓN DEL PROYECTO DE RECONVERSIÓN Y OPTIMIZACIÓN DEL ALUMBRADO PÚBLICO DE LA CIUDAD DE COLÓN”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Martes 13 DE OCTUBRE DEL AÑO 2026.- Hora: 10:30 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD</t>
+          <t>14 de OCTUBRE de 2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1603,7 +1607,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-059239b424b9c936</t>
+          <t>id-9e122d52de12ffef</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1624,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE COLON</t>
+          <t>DIAMANTE — COMUNA ALDEA PROTESTANTE -- DIAMANTE -- ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1633,10 +1637,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES ELÉCTRICOS PARA EJECUCIÓN DEL PROYECTO DE RECONVERSIÓN Y OPTIMIZACIÓN DEL ALUMBRADO PÚBLICO DE LA CIUDAD DE COLÓN”</t>
+          <t>Conforme a lo autorizado por decreto Nº 290/26 llámese a licitación pública Nº 03/26 con el objeto de comprar 10 toneladas de emulsión catiónica súper estable (asfalto de imprimación), puesto en Aldea Protestante</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1646,7 +1654,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>14 de OCTUBRE de 2026</t>
+          <t>miércoles 14 de octubre de 2026 – Hora nueve (09:00) Lugar de presentación de la oferta: Sede Comuna Aldea Protestan</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1654,11 +1662,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1676,7 +1680,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-9e122d52de12ffef</t>
+          <t>id-c2f3a25cfb37fd38</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1697,12 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DIAMANTE — COMUNA ALDEA PROTESTANTE -- DIAMANTE -- ENTRE RÍOS</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1708,12 +1712,12 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>03/2026</t>
+          <t>017/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Conforme a lo autorizado por decreto Nº 290/26 llámese a licitación pública Nº 03/26 con el objeto de comprar 10 toneladas de emulsión catiónica súper estable (asfalto de imprimación), puesto en Aldea Protestante</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de UNA (1) MOTONIVELADORA, nueva, sin uso, cero km, con una potencia entre 220/240 HP, con opción a implementos, que será utilizada para el área del corralón municipal</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1723,7 +1727,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>miércoles 14 de octubre de 2026 – Hora nueve (09:00) Lugar de presentación de la oferta: Sede Comuna Aldea Protestan</t>
+          <t>14 DE OCTUBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1731,7 +1735,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>$100.000,00. - (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1749,7 +1757,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-c2f3a25cfb37fd38</t>
+          <t>id-4c3b33859e5